--- a/光伏配储项目/电价数据/2026/丽晶站.xlsx
+++ b/光伏配储项目/电价数据/2026/丽晶站.xlsx
@@ -16,10 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy/mm/dd"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -64,7 +63,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,13 +429,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CS116"/>
+  <dimension ref="A1:CS143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>日期</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -34613,6 +34612,7917 @@
       </c>
       <c r="CS116" t="n">
         <v>0.75574</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="B117" t="n">
+        <v>0.38461</v>
+      </c>
+      <c r="C117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="D117" t="n">
+        <v>0.84537</v>
+      </c>
+      <c r="E117" t="n">
+        <v>0.5919500000000001</v>
+      </c>
+      <c r="F117" t="n">
+        <v>0.72401</v>
+      </c>
+      <c r="G117" t="n">
+        <v>1.10025</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0.44222</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0.45981</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0.43194</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0.42662</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0.42492</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0.41287</v>
+      </c>
+      <c r="N117" t="n">
+        <v>0.40048</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0.39994</v>
+      </c>
+      <c r="P117" t="n">
+        <v>0.38778</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>0.40473</v>
+      </c>
+      <c r="R117" t="n">
+        <v>0.42806</v>
+      </c>
+      <c r="S117" t="n">
+        <v>0.41666</v>
+      </c>
+      <c r="T117" t="n">
+        <v>0.35565</v>
+      </c>
+      <c r="U117" t="n">
+        <v>0.39469</v>
+      </c>
+      <c r="V117" t="n">
+        <v>0.38784</v>
+      </c>
+      <c r="W117" t="n">
+        <v>0.42053</v>
+      </c>
+      <c r="X117" t="n">
+        <v>0.39509</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>0.4244</v>
+      </c>
+      <c r="Z117" t="n">
+        <v>0.41744</v>
+      </c>
+      <c r="AA117" t="n">
+        <v>0.42759</v>
+      </c>
+      <c r="AB117" t="n">
+        <v>0.41517</v>
+      </c>
+      <c r="AC117" t="n">
+        <v>0.44736</v>
+      </c>
+      <c r="AD117" t="n">
+        <v>0.50195</v>
+      </c>
+      <c r="AE117" t="n">
+        <v>0.30002</v>
+      </c>
+      <c r="AF117" t="n">
+        <v>0.40082</v>
+      </c>
+      <c r="AG117" t="n">
+        <v>0.30827</v>
+      </c>
+      <c r="AH117" t="n">
+        <v>0.31177</v>
+      </c>
+      <c r="AI117" t="n">
+        <v>0.32796</v>
+      </c>
+      <c r="AJ117" t="n">
+        <v>0.35113</v>
+      </c>
+      <c r="AK117" t="n">
+        <v>0.37442</v>
+      </c>
+      <c r="AL117" t="n">
+        <v>0.32286</v>
+      </c>
+      <c r="AM117" t="n">
+        <v>0.34932</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>0.12546</v>
+      </c>
+      <c r="AO117" t="n">
+        <v>0.138</v>
+      </c>
+      <c r="AP117" t="n">
+        <v>0.33406</v>
+      </c>
+      <c r="AQ117" t="n">
+        <v>0.14367</v>
+      </c>
+      <c r="AR117" t="n">
+        <v>0.07751000000000001</v>
+      </c>
+      <c r="AS117" t="n">
+        <v>0.11689</v>
+      </c>
+      <c r="AT117" t="n">
+        <v>0.46563</v>
+      </c>
+      <c r="AU117" t="n">
+        <v>0.20188</v>
+      </c>
+      <c r="AV117" t="n">
+        <v>0.31082</v>
+      </c>
+      <c r="AW117" t="n">
+        <v>0.28741</v>
+      </c>
+      <c r="AX117" t="n">
+        <v>0.05151</v>
+      </c>
+      <c r="AY117" t="n">
+        <v>0.84221</v>
+      </c>
+      <c r="AZ117" t="n">
+        <v>1.32154</v>
+      </c>
+      <c r="BA117" t="n">
+        <v>0.14827</v>
+      </c>
+      <c r="BB117" t="n">
+        <v>0.21984</v>
+      </c>
+      <c r="BC117" t="n">
+        <v>0.22997</v>
+      </c>
+      <c r="BD117" t="n">
+        <v>0.23533</v>
+      </c>
+      <c r="BE117" t="n">
+        <v>0.21917</v>
+      </c>
+      <c r="BF117" t="n">
+        <v>0.74553</v>
+      </c>
+      <c r="BG117" t="n">
+        <v>0.26167</v>
+      </c>
+      <c r="BH117" t="n">
+        <v>0.44029</v>
+      </c>
+      <c r="BI117" t="n">
+        <v>0.15161</v>
+      </c>
+      <c r="BJ117" t="n">
+        <v>0.33496</v>
+      </c>
+      <c r="BK117" t="n">
+        <v>0.34854</v>
+      </c>
+      <c r="BL117" t="n">
+        <v>0.29086</v>
+      </c>
+      <c r="BM117" t="n">
+        <v>0.29261</v>
+      </c>
+      <c r="BN117" t="n">
+        <v>0.46922</v>
+      </c>
+      <c r="BO117" t="n">
+        <v>0.63847</v>
+      </c>
+      <c r="BP117" t="n">
+        <v>0.73034</v>
+      </c>
+      <c r="BQ117" t="n">
+        <v>0.97027</v>
+      </c>
+      <c r="BR117" t="n">
+        <v>0.7310599999999999</v>
+      </c>
+      <c r="BS117" t="n">
+        <v>1.67815</v>
+      </c>
+      <c r="BT117" t="n">
+        <v>0.39449</v>
+      </c>
+      <c r="BU117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BV117" t="n">
+        <v>0.43133</v>
+      </c>
+      <c r="BW117" t="n">
+        <v>0.43644</v>
+      </c>
+      <c r="BX117" t="n">
+        <v>0.6581399999999999</v>
+      </c>
+      <c r="BY117" t="n">
+        <v>1.31171</v>
+      </c>
+      <c r="BZ117" t="n">
+        <v>0.9195399999999999</v>
+      </c>
+      <c r="CA117" t="n">
+        <v>1.64843</v>
+      </c>
+      <c r="CB117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CC117" t="n">
+        <v>1.4962</v>
+      </c>
+      <c r="CD117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CE117" t="n">
+        <v>1.72877</v>
+      </c>
+      <c r="CF117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CG117" t="n">
+        <v>0.88773</v>
+      </c>
+      <c r="CH117" t="n">
+        <v>1.13107</v>
+      </c>
+      <c r="CI117" t="n">
+        <v>1.18736</v>
+      </c>
+      <c r="CJ117" t="n">
+        <v>1.66405</v>
+      </c>
+      <c r="CK117" t="n">
+        <v>1.2649</v>
+      </c>
+      <c r="CL117" t="n">
+        <v>0.8699199999999999</v>
+      </c>
+      <c r="CM117" t="n">
+        <v>0.79635</v>
+      </c>
+      <c r="CN117" t="n">
+        <v>0.7569400000000001</v>
+      </c>
+      <c r="CO117" t="n">
+        <v>0.5179199999999999</v>
+      </c>
+      <c r="CP117" t="n">
+        <v>0.47939</v>
+      </c>
+      <c r="CQ117" t="n">
+        <v>0.46935</v>
+      </c>
+      <c r="CR117" t="n">
+        <v>0.41567</v>
+      </c>
+      <c r="CS117" t="n">
+        <v>0.4253</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B118" t="n">
+        <v>0.32887</v>
+      </c>
+      <c r="C118" t="n">
+        <v>0.70809</v>
+      </c>
+      <c r="D118" t="n">
+        <v>1.76598</v>
+      </c>
+      <c r="E118" t="n">
+        <v>0.87025</v>
+      </c>
+      <c r="F118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G118" t="n">
+        <v>0.9146299999999999</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0.49386</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0.5143300000000001</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0.5023</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0.50254</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0.48482</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0.39922</v>
+      </c>
+      <c r="N118" t="n">
+        <v>0.46696</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0.37796</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0.37804</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>0.37747</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0.33621</v>
+      </c>
+      <c r="S118" t="n">
+        <v>0.36579</v>
+      </c>
+      <c r="T118" t="n">
+        <v>0.35122</v>
+      </c>
+      <c r="U118" t="n">
+        <v>0.35115</v>
+      </c>
+      <c r="V118" t="n">
+        <v>0.36344</v>
+      </c>
+      <c r="W118" t="n">
+        <v>0.36721</v>
+      </c>
+      <c r="X118" t="n">
+        <v>0.35067</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>0.37337</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>0.40687</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>0.8676699999999999</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>0.7111799999999999</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>0.80649</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>0.45504</v>
+      </c>
+      <c r="AE118" t="n">
+        <v>0.43599</v>
+      </c>
+      <c r="AF118" t="n">
+        <v>0.37698</v>
+      </c>
+      <c r="AG118" t="n">
+        <v>0.34747</v>
+      </c>
+      <c r="AH118" t="n">
+        <v>0.38703</v>
+      </c>
+      <c r="AI118" t="n">
+        <v>0.42659</v>
+      </c>
+      <c r="AJ118" t="n">
+        <v>0.5087699999999999</v>
+      </c>
+      <c r="AK118" t="n">
+        <v>0.35619</v>
+      </c>
+      <c r="AL118" t="n">
+        <v>0.33949</v>
+      </c>
+      <c r="AM118" t="n">
+        <v>0.3567</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>0.33239</v>
+      </c>
+      <c r="AO118" t="n">
+        <v>0.32923</v>
+      </c>
+      <c r="AP118" t="n">
+        <v>0.3745</v>
+      </c>
+      <c r="AQ118" t="n">
+        <v>0.30228</v>
+      </c>
+      <c r="AR118" t="n">
+        <v>0.33212</v>
+      </c>
+      <c r="AS118" t="n">
+        <v>0.3403</v>
+      </c>
+      <c r="AT118" t="n">
+        <v>0.37513</v>
+      </c>
+      <c r="AU118" t="n">
+        <v>0.50863</v>
+      </c>
+      <c r="AV118" t="n">
+        <v>0.7802899999999999</v>
+      </c>
+      <c r="AW118" t="n">
+        <v>0.99461</v>
+      </c>
+      <c r="AX118" t="n">
+        <v>0.33346</v>
+      </c>
+      <c r="AY118" t="n">
+        <v>0.52555</v>
+      </c>
+      <c r="AZ118" t="n">
+        <v>0.8951399999999999</v>
+      </c>
+      <c r="BA118" t="n">
+        <v>0.8503999999999999</v>
+      </c>
+      <c r="BB118" t="n">
+        <v>0.50076</v>
+      </c>
+      <c r="BC118" t="n">
+        <v>0.72693</v>
+      </c>
+      <c r="BD118" t="n">
+        <v>1.3986</v>
+      </c>
+      <c r="BE118" t="n">
+        <v>1.08757</v>
+      </c>
+      <c r="BF118" t="n">
+        <v>1.0332</v>
+      </c>
+      <c r="BG118" t="n">
+        <v>0.29531</v>
+      </c>
+      <c r="BH118" t="n">
+        <v>0.35187</v>
+      </c>
+      <c r="BI118" t="n">
+        <v>0.37499</v>
+      </c>
+      <c r="BJ118" t="n">
+        <v>0.4726</v>
+      </c>
+      <c r="BK118" t="n">
+        <v>0.54679</v>
+      </c>
+      <c r="BL118" t="n">
+        <v>0.49982</v>
+      </c>
+      <c r="BM118" t="n">
+        <v>0.52475</v>
+      </c>
+      <c r="BN118" t="n">
+        <v>0.9070199999999999</v>
+      </c>
+      <c r="BO118" t="n">
+        <v>0.62486</v>
+      </c>
+      <c r="BP118" t="n">
+        <v>0.89703</v>
+      </c>
+      <c r="BQ118" t="n">
+        <v>1.1697</v>
+      </c>
+      <c r="BR118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BS118" t="n">
+        <v>1.43451</v>
+      </c>
+      <c r="BT118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BU118" t="n">
+        <v>1.18073</v>
+      </c>
+      <c r="BV118" t="n">
+        <v>1.04374</v>
+      </c>
+      <c r="BW118" t="n">
+        <v>1.48069</v>
+      </c>
+      <c r="BX118" t="n">
+        <v>1.38285</v>
+      </c>
+      <c r="BY118" t="n">
+        <v>1.53826</v>
+      </c>
+      <c r="BZ118" t="n">
+        <v>1.31726</v>
+      </c>
+      <c r="CA118" t="n">
+        <v>1.36781</v>
+      </c>
+      <c r="CB118" t="n">
+        <v>0.9241699999999999</v>
+      </c>
+      <c r="CC118" t="n">
+        <v>1.26025</v>
+      </c>
+      <c r="CD118" t="n">
+        <v>0.90151</v>
+      </c>
+      <c r="CE118" t="n">
+        <v>1.32328</v>
+      </c>
+      <c r="CF118" t="n">
+        <v>1.36819</v>
+      </c>
+      <c r="CG118" t="n">
+        <v>1.25226</v>
+      </c>
+      <c r="CH118" t="n">
+        <v>1.04667</v>
+      </c>
+      <c r="CI118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CJ118" t="n">
+        <v>0.45019</v>
+      </c>
+      <c r="CK118" t="n">
+        <v>0.7885800000000001</v>
+      </c>
+      <c r="CL118" t="n">
+        <v>0.8085</v>
+      </c>
+      <c r="CM118" t="n">
+        <v>0.4489</v>
+      </c>
+      <c r="CN118" t="n">
+        <v>0.42805</v>
+      </c>
+      <c r="CO118" t="n">
+        <v>0.44356</v>
+      </c>
+      <c r="CP118" t="n">
+        <v>0.33361</v>
+      </c>
+      <c r="CQ118" t="n">
+        <v>0.37559</v>
+      </c>
+      <c r="CR118" t="n">
+        <v>0.35466</v>
+      </c>
+      <c r="CS118" t="n">
+        <v>0.33459</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B119" t="n">
+        <v>0.32142</v>
+      </c>
+      <c r="C119" t="n">
+        <v>0.50748</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0.48641</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0.48723</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0.37902</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0.448</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0.41411</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0.36861</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0.38911</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0.38262</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0.36305</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0.42749</v>
+      </c>
+      <c r="N119" t="n">
+        <v>0.4429</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0.33569</v>
+      </c>
+      <c r="P119" t="n">
+        <v>0.36997</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>0.39537</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0.36677</v>
+      </c>
+      <c r="S119" t="n">
+        <v>0.36765</v>
+      </c>
+      <c r="T119" t="n">
+        <v>0.35557</v>
+      </c>
+      <c r="U119" t="n">
+        <v>0.36103</v>
+      </c>
+      <c r="V119" t="n">
+        <v>0.35161</v>
+      </c>
+      <c r="W119" t="n">
+        <v>0.36288</v>
+      </c>
+      <c r="X119" t="n">
+        <v>0.35698</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>0.38321</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>0.39492</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>0.47185</v>
+      </c>
+      <c r="AB119" t="n">
+        <v>0.44382</v>
+      </c>
+      <c r="AC119" t="n">
+        <v>0.43769</v>
+      </c>
+      <c r="AD119" t="n">
+        <v>0.34728</v>
+      </c>
+      <c r="AE119" t="n">
+        <v>0.39417</v>
+      </c>
+      <c r="AF119" t="n">
+        <v>0.35268</v>
+      </c>
+      <c r="AG119" t="n">
+        <v>0.36726</v>
+      </c>
+      <c r="AH119" t="n">
+        <v>0.34736</v>
+      </c>
+      <c r="AI119" t="n">
+        <v>0.45658</v>
+      </c>
+      <c r="AJ119" t="n">
+        <v>0.58175</v>
+      </c>
+      <c r="AK119" t="n">
+        <v>0.7868200000000001</v>
+      </c>
+      <c r="AL119" t="n">
+        <v>0.7321799999999999</v>
+      </c>
+      <c r="AM119" t="n">
+        <v>0.66544</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>0.24304</v>
+      </c>
+      <c r="AO119" t="n">
+        <v>0.37841</v>
+      </c>
+      <c r="AP119" t="n">
+        <v>0.36775</v>
+      </c>
+      <c r="AQ119" t="n">
+        <v>0.33117</v>
+      </c>
+      <c r="AR119" t="n">
+        <v>0.36812</v>
+      </c>
+      <c r="AS119" t="n">
+        <v>0.39811</v>
+      </c>
+      <c r="AT119" t="n">
+        <v>0.41211</v>
+      </c>
+      <c r="AU119" t="n">
+        <v>0.55851</v>
+      </c>
+      <c r="AV119" t="n">
+        <v>0.50115</v>
+      </c>
+      <c r="AW119" t="n">
+        <v>0.82569</v>
+      </c>
+      <c r="AX119" t="n">
+        <v>0.39836</v>
+      </c>
+      <c r="AY119" t="n">
+        <v>0.5962000000000001</v>
+      </c>
+      <c r="AZ119" t="n">
+        <v>0.72734</v>
+      </c>
+      <c r="BA119" t="n">
+        <v>0.8153899999999999</v>
+      </c>
+      <c r="BB119" t="n">
+        <v>0.53098</v>
+      </c>
+      <c r="BC119" t="n">
+        <v>0.5403300000000001</v>
+      </c>
+      <c r="BD119" t="n">
+        <v>0.80102</v>
+      </c>
+      <c r="BE119" t="n">
+        <v>1.13563</v>
+      </c>
+      <c r="BF119" t="n">
+        <v>0.67775</v>
+      </c>
+      <c r="BG119" t="n">
+        <v>0.6011</v>
+      </c>
+      <c r="BH119" t="n">
+        <v>0.49399</v>
+      </c>
+      <c r="BI119" t="n">
+        <v>0.45057</v>
+      </c>
+      <c r="BJ119" t="n">
+        <v>0.42529</v>
+      </c>
+      <c r="BK119" t="n">
+        <v>0.39544</v>
+      </c>
+      <c r="BL119" t="n">
+        <v>0.72521</v>
+      </c>
+      <c r="BM119" t="n">
+        <v>0.51642</v>
+      </c>
+      <c r="BN119" t="n">
+        <v>0.50542</v>
+      </c>
+      <c r="BO119" t="n">
+        <v>0.57043</v>
+      </c>
+      <c r="BP119" t="n">
+        <v>0.59601</v>
+      </c>
+      <c r="BQ119" t="n">
+        <v>0.54465</v>
+      </c>
+      <c r="BR119" t="n">
+        <v>0.56464</v>
+      </c>
+      <c r="BS119" t="n">
+        <v>1.26425</v>
+      </c>
+      <c r="BT119" t="n">
+        <v>0.61611</v>
+      </c>
+      <c r="BU119" t="n">
+        <v>1.20046</v>
+      </c>
+      <c r="BV119" t="n">
+        <v>0.50562</v>
+      </c>
+      <c r="BW119" t="n">
+        <v>0.52651</v>
+      </c>
+      <c r="BX119" t="n">
+        <v>0.56662</v>
+      </c>
+      <c r="BY119" t="n">
+        <v>0.87588</v>
+      </c>
+      <c r="BZ119" t="n">
+        <v>0.91177</v>
+      </c>
+      <c r="CA119" t="n">
+        <v>1.41916</v>
+      </c>
+      <c r="CB119" t="n">
+        <v>0.7124199999999999</v>
+      </c>
+      <c r="CC119" t="n">
+        <v>0.73766</v>
+      </c>
+      <c r="CD119" t="n">
+        <v>0.6013500000000001</v>
+      </c>
+      <c r="CE119" t="n">
+        <v>0.7982100000000001</v>
+      </c>
+      <c r="CF119" t="n">
+        <v>0.6099199999999999</v>
+      </c>
+      <c r="CG119" t="n">
+        <v>0.83423</v>
+      </c>
+      <c r="CH119" t="n">
+        <v>0.56269</v>
+      </c>
+      <c r="CI119" t="n">
+        <v>1.15349</v>
+      </c>
+      <c r="CJ119" t="n">
+        <v>0.8063400000000001</v>
+      </c>
+      <c r="CK119" t="n">
+        <v>0.56051</v>
+      </c>
+      <c r="CL119" t="n">
+        <v>0.4837</v>
+      </c>
+      <c r="CM119" t="n">
+        <v>0.6173500000000001</v>
+      </c>
+      <c r="CN119" t="n">
+        <v>0.50059</v>
+      </c>
+      <c r="CO119" t="n">
+        <v>0.45662</v>
+      </c>
+      <c r="CP119" t="n">
+        <v>0.39738</v>
+      </c>
+      <c r="CQ119" t="n">
+        <v>0.36206</v>
+      </c>
+      <c r="CR119" t="n">
+        <v>0.34849</v>
+      </c>
+      <c r="CS119" t="n">
+        <v>0.34194</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B120" t="n">
+        <v>0.31894</v>
+      </c>
+      <c r="C120" t="n">
+        <v>0.52246</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0.49316</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.44515</v>
+      </c>
+      <c r="F120" t="n">
+        <v>0.38906</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0.38909</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0.42196</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0.36688</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0.35877</v>
+      </c>
+      <c r="K120" t="n">
+        <v>0.38717</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0.38534</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0.36113</v>
+      </c>
+      <c r="N120" t="n">
+        <v>0.44848</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0.35964</v>
+      </c>
+      <c r="P120" t="n">
+        <v>0.34837</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>0.36271</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0.35723</v>
+      </c>
+      <c r="S120" t="n">
+        <v>0.3583</v>
+      </c>
+      <c r="T120" t="n">
+        <v>0.33729</v>
+      </c>
+      <c r="U120" t="n">
+        <v>0.33481</v>
+      </c>
+      <c r="V120" t="n">
+        <v>0.33138</v>
+      </c>
+      <c r="W120" t="n">
+        <v>0.33394</v>
+      </c>
+      <c r="X120" t="n">
+        <v>0.33127</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>0.34998</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>0.33888</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>0.35099</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>0.38488</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>0.38839</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>0.34831</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>0.37452</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>0.34386</v>
+      </c>
+      <c r="AG120" t="n">
+        <v>0.39307</v>
+      </c>
+      <c r="AH120" t="n">
+        <v>0.41563</v>
+      </c>
+      <c r="AI120" t="n">
+        <v>0.4965</v>
+      </c>
+      <c r="AJ120" t="n">
+        <v>0.3563</v>
+      </c>
+      <c r="AK120" t="n">
+        <v>0.65743</v>
+      </c>
+      <c r="AL120" t="n">
+        <v>0.34041</v>
+      </c>
+      <c r="AM120" t="n">
+        <v>0.55316</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>0.73268</v>
+      </c>
+      <c r="AO120" t="n">
+        <v>0.97329</v>
+      </c>
+      <c r="AP120" t="n">
+        <v>0.6782899999999999</v>
+      </c>
+      <c r="AQ120" t="n">
+        <v>0.74861</v>
+      </c>
+      <c r="AR120" t="n">
+        <v>1.12618</v>
+      </c>
+      <c r="AS120" t="n">
+        <v>0.5884400000000001</v>
+      </c>
+      <c r="AT120" t="n">
+        <v>1.23429</v>
+      </c>
+      <c r="AU120" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AV120" t="n">
+        <v>1.07478</v>
+      </c>
+      <c r="AW120" t="n">
+        <v>0.9857400000000001</v>
+      </c>
+      <c r="AX120" t="n">
+        <v>0.78551</v>
+      </c>
+      <c r="AY120" t="n">
+        <v>1.21617</v>
+      </c>
+      <c r="AZ120" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BA120" t="n">
+        <v>0.80965</v>
+      </c>
+      <c r="BB120" t="n">
+        <v>0.35102</v>
+      </c>
+      <c r="BC120" t="n">
+        <v>0.35705</v>
+      </c>
+      <c r="BD120" t="n">
+        <v>0.4465</v>
+      </c>
+      <c r="BE120" t="n">
+        <v>0.60314</v>
+      </c>
+      <c r="BF120" t="n">
+        <v>0.40412</v>
+      </c>
+      <c r="BG120" t="n">
+        <v>0.33768</v>
+      </c>
+      <c r="BH120" t="n">
+        <v>0.32125</v>
+      </c>
+      <c r="BI120" t="n">
+        <v>0.34814</v>
+      </c>
+      <c r="BJ120" t="n">
+        <v>0.48082</v>
+      </c>
+      <c r="BK120" t="n">
+        <v>0.40521</v>
+      </c>
+      <c r="BL120" t="n">
+        <v>0.39835</v>
+      </c>
+      <c r="BM120" t="n">
+        <v>0.7601100000000001</v>
+      </c>
+      <c r="BN120" t="n">
+        <v>0.76838</v>
+      </c>
+      <c r="BO120" t="n">
+        <v>0.6869500000000001</v>
+      </c>
+      <c r="BP120" t="n">
+        <v>1.18495</v>
+      </c>
+      <c r="BQ120" t="n">
+        <v>1.18646</v>
+      </c>
+      <c r="BR120" t="n">
+        <v>0.42681</v>
+      </c>
+      <c r="BS120" t="n">
+        <v>0.4944</v>
+      </c>
+      <c r="BT120" t="n">
+        <v>0.45017</v>
+      </c>
+      <c r="BU120" t="n">
+        <v>0.46147</v>
+      </c>
+      <c r="BV120" t="n">
+        <v>0.39947</v>
+      </c>
+      <c r="BW120" t="n">
+        <v>0.47395</v>
+      </c>
+      <c r="BX120" t="n">
+        <v>0.52044</v>
+      </c>
+      <c r="BY120" t="n">
+        <v>0.9032899999999999</v>
+      </c>
+      <c r="BZ120" t="n">
+        <v>0.79164</v>
+      </c>
+      <c r="CA120" t="n">
+        <v>1.20078</v>
+      </c>
+      <c r="CB120" t="n">
+        <v>0.84734</v>
+      </c>
+      <c r="CC120" t="n">
+        <v>0.76406</v>
+      </c>
+      <c r="CD120" t="n">
+        <v>0.5004</v>
+      </c>
+      <c r="CE120" t="n">
+        <v>0.6991000000000001</v>
+      </c>
+      <c r="CF120" t="n">
+        <v>0.6577000000000001</v>
+      </c>
+      <c r="CG120" t="n">
+        <v>0.57694</v>
+      </c>
+      <c r="CH120" t="n">
+        <v>0.41555</v>
+      </c>
+      <c r="CI120" t="n">
+        <v>0.48967</v>
+      </c>
+      <c r="CJ120" t="n">
+        <v>0.49175</v>
+      </c>
+      <c r="CK120" t="n">
+        <v>0.34627</v>
+      </c>
+      <c r="CL120" t="n">
+        <v>0.34139</v>
+      </c>
+      <c r="CM120" t="n">
+        <v>0.31904</v>
+      </c>
+      <c r="CN120" t="n">
+        <v>0.32306</v>
+      </c>
+      <c r="CO120" t="n">
+        <v>0.32042</v>
+      </c>
+      <c r="CP120" t="n">
+        <v>0.31414</v>
+      </c>
+      <c r="CQ120" t="n">
+        <v>0.31814</v>
+      </c>
+      <c r="CR120" t="n">
+        <v>0.31995</v>
+      </c>
+      <c r="CS120" t="n">
+        <v>0.31749</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B121" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="C121" t="n">
+        <v>0.66396</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0.7591100000000001</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0.38237</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0.36141</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0.35935</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0.3293</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0.32811</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0.3323</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0.32079</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0.31905</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0.31613</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0.3189</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0.31848</v>
+      </c>
+      <c r="P121" t="n">
+        <v>0.31515</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>0.31635</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0.31309</v>
+      </c>
+      <c r="S121" t="n">
+        <v>0.31448</v>
+      </c>
+      <c r="T121" t="n">
+        <v>0.31965</v>
+      </c>
+      <c r="U121" t="n">
+        <v>0.31609</v>
+      </c>
+      <c r="V121" t="n">
+        <v>0.31089</v>
+      </c>
+      <c r="W121" t="n">
+        <v>0.31025</v>
+      </c>
+      <c r="X121" t="n">
+        <v>0.3134</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>0.3147</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>0.31646</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>0.32452</v>
+      </c>
+      <c r="AB121" t="n">
+        <v>0.32434</v>
+      </c>
+      <c r="AC121" t="n">
+        <v>0.3326</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>0.32612</v>
+      </c>
+      <c r="AE121" t="n">
+        <v>0.32141</v>
+      </c>
+      <c r="AF121" t="n">
+        <v>0.32287</v>
+      </c>
+      <c r="AG121" t="n">
+        <v>0.32253</v>
+      </c>
+      <c r="AH121" t="n">
+        <v>0.33463</v>
+      </c>
+      <c r="AI121" t="n">
+        <v>0.4294</v>
+      </c>
+      <c r="AJ121" t="n">
+        <v>0.31468</v>
+      </c>
+      <c r="AK121" t="n">
+        <v>0.28649</v>
+      </c>
+      <c r="AL121" t="n">
+        <v>0.33263</v>
+      </c>
+      <c r="AM121" t="n">
+        <v>0.32769</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>0.30758</v>
+      </c>
+      <c r="AO121" t="n">
+        <v>0.31869</v>
+      </c>
+      <c r="AP121" t="n">
+        <v>0.30379</v>
+      </c>
+      <c r="AQ121" t="n">
+        <v>0.30746</v>
+      </c>
+      <c r="AR121" t="n">
+        <v>0.20279</v>
+      </c>
+      <c r="AS121" t="n">
+        <v>0.46089</v>
+      </c>
+      <c r="AT121" t="n">
+        <v>0.43245</v>
+      </c>
+      <c r="AU121" t="n">
+        <v>0.2246</v>
+      </c>
+      <c r="AV121" t="n">
+        <v>0.15733</v>
+      </c>
+      <c r="AW121" t="n">
+        <v>0.29022</v>
+      </c>
+      <c r="AX121" t="n">
+        <v>0.39971</v>
+      </c>
+      <c r="AY121" t="n">
+        <v>0.40855</v>
+      </c>
+      <c r="AZ121" t="n">
+        <v>0.27365</v>
+      </c>
+      <c r="BA121" t="n">
+        <v>0.18951</v>
+      </c>
+      <c r="BB121" t="n">
+        <v>0.53615</v>
+      </c>
+      <c r="BC121" t="n">
+        <v>0.50693</v>
+      </c>
+      <c r="BD121" t="n">
+        <v>0.05512</v>
+      </c>
+      <c r="BE121" t="n">
+        <v>0.38316</v>
+      </c>
+      <c r="BF121" t="n">
+        <v>0.38069</v>
+      </c>
+      <c r="BG121" t="n">
+        <v>0.22451</v>
+      </c>
+      <c r="BH121" t="n">
+        <v>0.45748</v>
+      </c>
+      <c r="BI121" t="n">
+        <v>0.21297</v>
+      </c>
+      <c r="BJ121" t="n">
+        <v>0.06387</v>
+      </c>
+      <c r="BK121" t="n">
+        <v>0.11047</v>
+      </c>
+      <c r="BL121" t="n">
+        <v>0.004059999999999999</v>
+      </c>
+      <c r="BM121" t="n">
+        <v>0.00319</v>
+      </c>
+      <c r="BN121" t="n">
+        <v>1.06876</v>
+      </c>
+      <c r="BO121" t="n">
+        <v>0.272</v>
+      </c>
+      <c r="BP121" t="n">
+        <v>0.29766</v>
+      </c>
+      <c r="BQ121" t="n">
+        <v>0.30001</v>
+      </c>
+      <c r="BR121" t="n">
+        <v>0.30811</v>
+      </c>
+      <c r="BS121" t="n">
+        <v>0.33148</v>
+      </c>
+      <c r="BT121" t="n">
+        <v>0.31961</v>
+      </c>
+      <c r="BU121" t="n">
+        <v>0.31995</v>
+      </c>
+      <c r="BV121" t="n">
+        <v>0.32957</v>
+      </c>
+      <c r="BW121" t="n">
+        <v>0.31546</v>
+      </c>
+      <c r="BX121" t="n">
+        <v>0.33545</v>
+      </c>
+      <c r="BY121" t="n">
+        <v>0.33572</v>
+      </c>
+      <c r="BZ121" t="n">
+        <v>0.33586</v>
+      </c>
+      <c r="CA121" t="n">
+        <v>0.33342</v>
+      </c>
+      <c r="CB121" t="n">
+        <v>0.37665</v>
+      </c>
+      <c r="CC121" t="n">
+        <v>0.38234</v>
+      </c>
+      <c r="CD121" t="n">
+        <v>0.37691</v>
+      </c>
+      <c r="CE121" t="n">
+        <v>0.37109</v>
+      </c>
+      <c r="CF121" t="n">
+        <v>0.35731</v>
+      </c>
+      <c r="CG121" t="n">
+        <v>0.38853</v>
+      </c>
+      <c r="CH121" t="n">
+        <v>0.39177</v>
+      </c>
+      <c r="CI121" t="n">
+        <v>0.40044</v>
+      </c>
+      <c r="CJ121" t="n">
+        <v>0.46072</v>
+      </c>
+      <c r="CK121" t="n">
+        <v>0.37062</v>
+      </c>
+      <c r="CL121" t="n">
+        <v>0.38995</v>
+      </c>
+      <c r="CM121" t="n">
+        <v>0.39157</v>
+      </c>
+      <c r="CN121" t="n">
+        <v>0.48496</v>
+      </c>
+      <c r="CO121" t="n">
+        <v>0.3522</v>
+      </c>
+      <c r="CP121" t="n">
+        <v>0.35664</v>
+      </c>
+      <c r="CQ121" t="n">
+        <v>0.34434</v>
+      </c>
+      <c r="CR121" t="n">
+        <v>0.35382</v>
+      </c>
+      <c r="CS121" t="n">
+        <v>0.34366</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B122" t="n">
+        <v>0.36605</v>
+      </c>
+      <c r="C122" t="n">
+        <v>0.58385</v>
+      </c>
+      <c r="D122" t="n">
+        <v>0.37853</v>
+      </c>
+      <c r="E122" t="n">
+        <v>0.40175</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0.3852</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0.37986</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0.35149</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0.3435299999999999</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0.35092</v>
+      </c>
+      <c r="K122" t="n">
+        <v>0.30217</v>
+      </c>
+      <c r="L122" t="n">
+        <v>0.30029</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0.28487</v>
+      </c>
+      <c r="N122" t="n">
+        <v>0.33256</v>
+      </c>
+      <c r="O122" t="n">
+        <v>0.2639</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0.34072</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>0.33764</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0.32854</v>
+      </c>
+      <c r="S122" t="n">
+        <v>0.2827</v>
+      </c>
+      <c r="T122" t="n">
+        <v>0.31234</v>
+      </c>
+      <c r="U122" t="n">
+        <v>0.3092200000000001</v>
+      </c>
+      <c r="V122" t="n">
+        <v>0.29431</v>
+      </c>
+      <c r="W122" t="n">
+        <v>0.29152</v>
+      </c>
+      <c r="X122" t="n">
+        <v>0.2903</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>0.32884</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>0.31941</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>0.33285</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>0.3455299999999999</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>0.31191</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>0.30544</v>
+      </c>
+      <c r="AE122" t="n">
+        <v>0.10251</v>
+      </c>
+      <c r="AF122" t="n">
+        <v>0.10277</v>
+      </c>
+      <c r="AG122" t="n">
+        <v>0.04358</v>
+      </c>
+      <c r="AH122" t="n">
+        <v>-0.04697999999999999</v>
+      </c>
+      <c r="AI122" t="n">
+        <v>-0.04574</v>
+      </c>
+      <c r="AJ122" t="n">
+        <v>-0.04621</v>
+      </c>
+      <c r="AK122" t="n">
+        <v>-0.0441</v>
+      </c>
+      <c r="AL122" t="n">
+        <v>-0.04621</v>
+      </c>
+      <c r="AM122" t="n">
+        <v>-0.04475</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>-0.04398</v>
+      </c>
+      <c r="AO122" t="n">
+        <v>0.36304</v>
+      </c>
+      <c r="AP122" t="n">
+        <v>0.01613</v>
+      </c>
+      <c r="AQ122" t="n">
+        <v>0.21788</v>
+      </c>
+      <c r="AR122" t="n">
+        <v>0.05508</v>
+      </c>
+      <c r="AS122" t="n">
+        <v>0.29264</v>
+      </c>
+      <c r="AT122" t="n">
+        <v>0.20914</v>
+      </c>
+      <c r="AU122" t="n">
+        <v>0.07312</v>
+      </c>
+      <c r="AV122" t="n">
+        <v>-0.04392</v>
+      </c>
+      <c r="AW122" t="n">
+        <v>-0.04394</v>
+      </c>
+      <c r="AX122" t="n">
+        <v>-0.04574</v>
+      </c>
+      <c r="AY122" t="n">
+        <v>-0.0456</v>
+      </c>
+      <c r="AZ122" t="n">
+        <v>-0.04561</v>
+      </c>
+      <c r="BA122" t="n">
+        <v>-0.04369</v>
+      </c>
+      <c r="BB122" t="n">
+        <v>-0.04335</v>
+      </c>
+      <c r="BC122" t="n">
+        <v>-0.04549</v>
+      </c>
+      <c r="BD122" t="n">
+        <v>-0.04339</v>
+      </c>
+      <c r="BE122" t="n">
+        <v>0.37576</v>
+      </c>
+      <c r="BF122" t="n">
+        <v>-0.04529</v>
+      </c>
+      <c r="BG122" t="n">
+        <v>-0.04525</v>
+      </c>
+      <c r="BH122" t="n">
+        <v>-0.04538</v>
+      </c>
+      <c r="BI122" t="n">
+        <v>-0.04358</v>
+      </c>
+      <c r="BJ122" t="n">
+        <v>-0.04423</v>
+      </c>
+      <c r="BK122" t="n">
+        <v>0.07202</v>
+      </c>
+      <c r="BL122" t="n">
+        <v>0.07027</v>
+      </c>
+      <c r="BM122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN122" t="n">
+        <v>-0.04471</v>
+      </c>
+      <c r="BO122" t="n">
+        <v>-0.04997</v>
+      </c>
+      <c r="BP122" t="n">
+        <v>-0.04984</v>
+      </c>
+      <c r="BQ122" t="n">
+        <v>-0.0474</v>
+      </c>
+      <c r="BR122" t="n">
+        <v>-0.04790999999999999</v>
+      </c>
+      <c r="BS122" t="n">
+        <v>0.19975</v>
+      </c>
+      <c r="BT122" t="n">
+        <v>0.14272</v>
+      </c>
+      <c r="BU122" t="n">
+        <v>0.28994</v>
+      </c>
+      <c r="BV122" t="n">
+        <v>0.29465</v>
+      </c>
+      <c r="BW122" t="n">
+        <v>0.30454</v>
+      </c>
+      <c r="BX122" t="n">
+        <v>0.29982</v>
+      </c>
+      <c r="BY122" t="n">
+        <v>0.29492</v>
+      </c>
+      <c r="BZ122" t="n">
+        <v>0.29282</v>
+      </c>
+      <c r="CA122" t="n">
+        <v>0.29329</v>
+      </c>
+      <c r="CB122" t="n">
+        <v>0.29225</v>
+      </c>
+      <c r="CC122" t="n">
+        <v>0.29678</v>
+      </c>
+      <c r="CD122" t="n">
+        <v>0.29074</v>
+      </c>
+      <c r="CE122" t="n">
+        <v>0.29497</v>
+      </c>
+      <c r="CF122" t="n">
+        <v>0.26875</v>
+      </c>
+      <c r="CG122" t="n">
+        <v>0.29381</v>
+      </c>
+      <c r="CH122" t="n">
+        <v>0.29802</v>
+      </c>
+      <c r="CI122" t="n">
+        <v>0.30855</v>
+      </c>
+      <c r="CJ122" t="n">
+        <v>0.30375</v>
+      </c>
+      <c r="CK122" t="n">
+        <v>0.30221</v>
+      </c>
+      <c r="CL122" t="n">
+        <v>0.31434</v>
+      </c>
+      <c r="CM122" t="n">
+        <v>0.31839</v>
+      </c>
+      <c r="CN122" t="n">
+        <v>0.34712</v>
+      </c>
+      <c r="CO122" t="n">
+        <v>0.34715</v>
+      </c>
+      <c r="CP122" t="n">
+        <v>0.34024</v>
+      </c>
+      <c r="CQ122" t="n">
+        <v>0.36031</v>
+      </c>
+      <c r="CR122" t="n">
+        <v>0.35989</v>
+      </c>
+      <c r="CS122" t="n">
+        <v>0.33117</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="B123" t="n">
+        <v>0.32419</v>
+      </c>
+      <c r="C123" t="n">
+        <v>1.31257</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0.31031</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.3947</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0.34488</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0.32034</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0.30704</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0.31463</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0.30134</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0.28114</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0.29441</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0.29069</v>
+      </c>
+      <c r="N123" t="n">
+        <v>0.28802</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0.28084</v>
+      </c>
+      <c r="P123" t="n">
+        <v>0.27116</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>0.27089</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0.2810299999999999</v>
+      </c>
+      <c r="S123" t="n">
+        <v>0.17236</v>
+      </c>
+      <c r="T123" t="n">
+        <v>0.1586</v>
+      </c>
+      <c r="U123" t="n">
+        <v>0.17092</v>
+      </c>
+      <c r="V123" t="n">
+        <v>0.1477</v>
+      </c>
+      <c r="W123" t="n">
+        <v>0.15943</v>
+      </c>
+      <c r="X123" t="n">
+        <v>0.15858</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>0.23612</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>0.214</v>
+      </c>
+      <c r="AA123" t="n">
+        <v>0.22651</v>
+      </c>
+      <c r="AB123" t="n">
+        <v>0.26883</v>
+      </c>
+      <c r="AC123" t="n">
+        <v>0.28566</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>0.29075</v>
+      </c>
+      <c r="AE123" t="n">
+        <v>0.31932</v>
+      </c>
+      <c r="AF123" t="n">
+        <v>0.28069</v>
+      </c>
+      <c r="AG123" t="n">
+        <v>0.28084</v>
+      </c>
+      <c r="AH123" t="n">
+        <v>0.2810299999999999</v>
+      </c>
+      <c r="AI123" t="n">
+        <v>0.28043</v>
+      </c>
+      <c r="AJ123" t="n">
+        <v>0.27071</v>
+      </c>
+      <c r="AK123" t="n">
+        <v>0.28091</v>
+      </c>
+      <c r="AL123" t="n">
+        <v>0.32236</v>
+      </c>
+      <c r="AM123" t="n">
+        <v>0.31015</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>0.30493</v>
+      </c>
+      <c r="AO123" t="n">
+        <v>0.3163</v>
+      </c>
+      <c r="AP123" t="n">
+        <v>0.30939</v>
+      </c>
+      <c r="AQ123" t="n">
+        <v>0.35894</v>
+      </c>
+      <c r="AR123" t="n">
+        <v>0.31626</v>
+      </c>
+      <c r="AS123" t="n">
+        <v>0.29732</v>
+      </c>
+      <c r="AT123" t="n">
+        <v>0.38716</v>
+      </c>
+      <c r="AU123" t="n">
+        <v>0.37943</v>
+      </c>
+      <c r="AV123" t="n">
+        <v>0.42751</v>
+      </c>
+      <c r="AW123" t="n">
+        <v>0.45525</v>
+      </c>
+      <c r="AX123" t="n">
+        <v>0.33182</v>
+      </c>
+      <c r="AY123" t="n">
+        <v>0.41845</v>
+      </c>
+      <c r="AZ123" t="n">
+        <v>0.41528</v>
+      </c>
+      <c r="BA123" t="n">
+        <v>0.38648</v>
+      </c>
+      <c r="BB123" t="n">
+        <v>0.40242</v>
+      </c>
+      <c r="BC123" t="n">
+        <v>0.30005</v>
+      </c>
+      <c r="BD123" t="n">
+        <v>0.30095</v>
+      </c>
+      <c r="BE123" t="n">
+        <v>0.2993</v>
+      </c>
+      <c r="BF123" t="n">
+        <v>0.29998</v>
+      </c>
+      <c r="BG123" t="n">
+        <v>0.15654</v>
+      </c>
+      <c r="BH123" t="n">
+        <v>0.29431</v>
+      </c>
+      <c r="BI123" t="n">
+        <v>0.31094</v>
+      </c>
+      <c r="BJ123" t="n">
+        <v>0.31343</v>
+      </c>
+      <c r="BK123" t="n">
+        <v>0.3127</v>
+      </c>
+      <c r="BL123" t="n">
+        <v>0.32184</v>
+      </c>
+      <c r="BM123" t="n">
+        <v>0.34628</v>
+      </c>
+      <c r="BN123" t="n">
+        <v>0.30067</v>
+      </c>
+      <c r="BO123" t="n">
+        <v>0.33083</v>
+      </c>
+      <c r="BP123" t="n">
+        <v>0.38546</v>
+      </c>
+      <c r="BQ123" t="n">
+        <v>0.47916</v>
+      </c>
+      <c r="BR123" t="n">
+        <v>0.5076700000000001</v>
+      </c>
+      <c r="BS123" t="n">
+        <v>0.79098</v>
+      </c>
+      <c r="BT123" t="n">
+        <v>0.6220399999999999</v>
+      </c>
+      <c r="BU123" t="n">
+        <v>0.78522</v>
+      </c>
+      <c r="BV123" t="n">
+        <v>0.40003</v>
+      </c>
+      <c r="BW123" t="n">
+        <v>0.49797</v>
+      </c>
+      <c r="BX123" t="n">
+        <v>0.7810199999999999</v>
+      </c>
+      <c r="BY123" t="n">
+        <v>0.92039</v>
+      </c>
+      <c r="BZ123" t="n">
+        <v>0.49456</v>
+      </c>
+      <c r="CA123" t="n">
+        <v>0.9142100000000001</v>
+      </c>
+      <c r="CB123" t="n">
+        <v>0.8628899999999999</v>
+      </c>
+      <c r="CC123" t="n">
+        <v>1.29622</v>
+      </c>
+      <c r="CD123" t="n">
+        <v>0.35366</v>
+      </c>
+      <c r="CE123" t="n">
+        <v>0.88751</v>
+      </c>
+      <c r="CF123" t="n">
+        <v>0.6316000000000001</v>
+      </c>
+      <c r="CG123" t="n">
+        <v>1.18709</v>
+      </c>
+      <c r="CH123" t="n">
+        <v>0.88085</v>
+      </c>
+      <c r="CI123" t="n">
+        <v>1.38914</v>
+      </c>
+      <c r="CJ123" t="n">
+        <v>1.33086</v>
+      </c>
+      <c r="CK123" t="n">
+        <v>1.03292</v>
+      </c>
+      <c r="CL123" t="n">
+        <v>0.5307999999999999</v>
+      </c>
+      <c r="CM123" t="n">
+        <v>0.79099</v>
+      </c>
+      <c r="CN123" t="n">
+        <v>0.85784</v>
+      </c>
+      <c r="CO123" t="n">
+        <v>0.77298</v>
+      </c>
+      <c r="CP123" t="n">
+        <v>0.77755</v>
+      </c>
+      <c r="CQ123" t="n">
+        <v>0.8767699999999999</v>
+      </c>
+      <c r="CR123" t="n">
+        <v>0.87387</v>
+      </c>
+      <c r="CS123" t="n">
+        <v>0.49316</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="B124" t="n">
+        <v>0.39868</v>
+      </c>
+      <c r="C124" t="n">
+        <v>1.3999</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0.44995</v>
+      </c>
+      <c r="E124" t="n">
+        <v>1.207</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0.87883</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0.55102</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0.62186</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0.53832</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0.49769</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0.45582</v>
+      </c>
+      <c r="L124" t="n">
+        <v>0.42425</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0.43714</v>
+      </c>
+      <c r="N124" t="n">
+        <v>0.44959</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0.38817</v>
+      </c>
+      <c r="P124" t="n">
+        <v>0.45268</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>0.41965</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0.34671</v>
+      </c>
+      <c r="S124" t="n">
+        <v>0.39839</v>
+      </c>
+      <c r="T124" t="n">
+        <v>0.36263</v>
+      </c>
+      <c r="U124" t="n">
+        <v>0.38343</v>
+      </c>
+      <c r="V124" t="n">
+        <v>0.40882</v>
+      </c>
+      <c r="W124" t="n">
+        <v>0.42603</v>
+      </c>
+      <c r="X124" t="n">
+        <v>0.33948</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>0.38676</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>0.34558</v>
+      </c>
+      <c r="AA124" t="n">
+        <v>0.3358</v>
+      </c>
+      <c r="AB124" t="n">
+        <v>0.32933</v>
+      </c>
+      <c r="AC124" t="n">
+        <v>0.33998</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>0.38376</v>
+      </c>
+      <c r="AE124" t="n">
+        <v>0.34745</v>
+      </c>
+      <c r="AF124" t="n">
+        <v>0.4492</v>
+      </c>
+      <c r="AG124" t="n">
+        <v>0.3464100000000001</v>
+      </c>
+      <c r="AH124" t="n">
+        <v>0.3922</v>
+      </c>
+      <c r="AI124" t="n">
+        <v>0.38304</v>
+      </c>
+      <c r="AJ124" t="n">
+        <v>0.5570700000000001</v>
+      </c>
+      <c r="AK124" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="AL124" t="n">
+        <v>0.5837</v>
+      </c>
+      <c r="AM124" t="n">
+        <v>0.70625</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>0.87627</v>
+      </c>
+      <c r="AO124" t="n">
+        <v>0.46634</v>
+      </c>
+      <c r="AP124" t="n">
+        <v>0.39034</v>
+      </c>
+      <c r="AQ124" t="n">
+        <v>0.55033</v>
+      </c>
+      <c r="AR124" t="n">
+        <v>0.43294</v>
+      </c>
+      <c r="AS124" t="n">
+        <v>0.8131900000000001</v>
+      </c>
+      <c r="AT124" t="n">
+        <v>0.56636</v>
+      </c>
+      <c r="AU124" t="n">
+        <v>0.85272</v>
+      </c>
+      <c r="AV124" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AW124" t="n">
+        <v>0.87498</v>
+      </c>
+      <c r="AX124" t="n">
+        <v>0.34135</v>
+      </c>
+      <c r="AY124" t="n">
+        <v>0.41758</v>
+      </c>
+      <c r="AZ124" t="n">
+        <v>0.62438</v>
+      </c>
+      <c r="BA124" t="n">
+        <v>0.32998</v>
+      </c>
+      <c r="BB124" t="n">
+        <v>0.30271</v>
+      </c>
+      <c r="BC124" t="n">
+        <v>0.29364</v>
+      </c>
+      <c r="BD124" t="n">
+        <v>0.6303300000000001</v>
+      </c>
+      <c r="BE124" t="n">
+        <v>0.59297</v>
+      </c>
+      <c r="BF124" t="n">
+        <v>1.32579</v>
+      </c>
+      <c r="BG124" t="n">
+        <v>0.31056</v>
+      </c>
+      <c r="BH124" t="n">
+        <v>0.35243</v>
+      </c>
+      <c r="BI124" t="n">
+        <v>0.33012</v>
+      </c>
+      <c r="BJ124" t="n">
+        <v>0.32079</v>
+      </c>
+      <c r="BK124" t="n">
+        <v>0.40648</v>
+      </c>
+      <c r="BL124" t="n">
+        <v>0.33408</v>
+      </c>
+      <c r="BM124" t="n">
+        <v>0.31709</v>
+      </c>
+      <c r="BN124" t="n">
+        <v>0.31954</v>
+      </c>
+      <c r="BO124" t="n">
+        <v>0.31908</v>
+      </c>
+      <c r="BP124" t="n">
+        <v>0.31952</v>
+      </c>
+      <c r="BQ124" t="n">
+        <v>0.33545</v>
+      </c>
+      <c r="BR124" t="n">
+        <v>0.31731</v>
+      </c>
+      <c r="BS124" t="n">
+        <v>0.30863</v>
+      </c>
+      <c r="BT124" t="n">
+        <v>0.31879</v>
+      </c>
+      <c r="BU124" t="n">
+        <v>0.3014</v>
+      </c>
+      <c r="BV124" t="n">
+        <v>0.29585</v>
+      </c>
+      <c r="BW124" t="n">
+        <v>0.31127</v>
+      </c>
+      <c r="BX124" t="n">
+        <v>0.30959</v>
+      </c>
+      <c r="BY124" t="n">
+        <v>0.31066</v>
+      </c>
+      <c r="BZ124" t="n">
+        <v>0.28596</v>
+      </c>
+      <c r="CA124" t="n">
+        <v>0.29985</v>
+      </c>
+      <c r="CB124" t="n">
+        <v>0.30366</v>
+      </c>
+      <c r="CC124" t="n">
+        <v>0.3125</v>
+      </c>
+      <c r="CD124" t="n">
+        <v>0.31002</v>
+      </c>
+      <c r="CE124" t="n">
+        <v>0.31524</v>
+      </c>
+      <c r="CF124" t="n">
+        <v>0.34788</v>
+      </c>
+      <c r="CG124" t="n">
+        <v>0.3301</v>
+      </c>
+      <c r="CH124" t="n">
+        <v>0.33382</v>
+      </c>
+      <c r="CI124" t="n">
+        <v>0.33171</v>
+      </c>
+      <c r="CJ124" t="n">
+        <v>0.32401</v>
+      </c>
+      <c r="CK124" t="n">
+        <v>0.32805</v>
+      </c>
+      <c r="CL124" t="n">
+        <v>0.32632</v>
+      </c>
+      <c r="CM124" t="n">
+        <v>0.38692</v>
+      </c>
+      <c r="CN124" t="n">
+        <v>0.38905</v>
+      </c>
+      <c r="CO124" t="n">
+        <v>0.42161</v>
+      </c>
+      <c r="CP124" t="n">
+        <v>0.39096</v>
+      </c>
+      <c r="CQ124" t="n">
+        <v>0.37306</v>
+      </c>
+      <c r="CR124" t="n">
+        <v>0.35681</v>
+      </c>
+      <c r="CS124" t="n">
+        <v>0.34692</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B125" t="n">
+        <v>0.32835</v>
+      </c>
+      <c r="C125" t="n">
+        <v>0.91354</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0.34915</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0.44281</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0.40675</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0.39275</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0.43569</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0.36593</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0.38898</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0.35168</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0.35464</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0.34029</v>
+      </c>
+      <c r="N125" t="n">
+        <v>0.33962</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0.33474</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0.32417</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>0.34785</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0.33608</v>
+      </c>
+      <c r="S125" t="n">
+        <v>0.31719</v>
+      </c>
+      <c r="T125" t="n">
+        <v>0.37643</v>
+      </c>
+      <c r="U125" t="n">
+        <v>0.45982</v>
+      </c>
+      <c r="V125" t="n">
+        <v>0.34566</v>
+      </c>
+      <c r="W125" t="n">
+        <v>0.36814</v>
+      </c>
+      <c r="X125" t="n">
+        <v>0.33357</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>0.33942</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>0.3428</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>0.35492</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>0.3454</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>0.34947</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>0.30703</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>0.30903</v>
+      </c>
+      <c r="AF125" t="n">
+        <v>0.32485</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>0.3293</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>0.331</v>
+      </c>
+      <c r="AI125" t="n">
+        <v>0.3406</v>
+      </c>
+      <c r="AJ125" t="n">
+        <v>0.31251</v>
+      </c>
+      <c r="AK125" t="n">
+        <v>0.3109</v>
+      </c>
+      <c r="AL125" t="n">
+        <v>0.28799</v>
+      </c>
+      <c r="AM125" t="n">
+        <v>0.31284</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>0.31267</v>
+      </c>
+      <c r="AO125" t="n">
+        <v>0.30107</v>
+      </c>
+      <c r="AP125" t="n">
+        <v>0.19085</v>
+      </c>
+      <c r="AQ125" t="n">
+        <v>0.30432</v>
+      </c>
+      <c r="AR125" t="n">
+        <v>0.30805</v>
+      </c>
+      <c r="AS125" t="n">
+        <v>0.34156</v>
+      </c>
+      <c r="AT125" t="n">
+        <v>0.33481</v>
+      </c>
+      <c r="AU125" t="n">
+        <v>0.36039</v>
+      </c>
+      <c r="AV125" t="n">
+        <v>0.31123</v>
+      </c>
+      <c r="AW125" t="n">
+        <v>0.27313</v>
+      </c>
+      <c r="AX125" t="n">
+        <v>0.19766</v>
+      </c>
+      <c r="AY125" t="n">
+        <v>0.30494</v>
+      </c>
+      <c r="AZ125" t="n">
+        <v>0.29874</v>
+      </c>
+      <c r="BA125" t="n">
+        <v>0.32011</v>
+      </c>
+      <c r="BB125" t="n">
+        <v>0.2814</v>
+      </c>
+      <c r="BC125" t="n">
+        <v>0.30899</v>
+      </c>
+      <c r="BD125" t="n">
+        <v>0.30944</v>
+      </c>
+      <c r="BE125" t="n">
+        <v>0.3479100000000001</v>
+      </c>
+      <c r="BF125" t="n">
+        <v>0.35608</v>
+      </c>
+      <c r="BG125" t="n">
+        <v>0.3083399999999999</v>
+      </c>
+      <c r="BH125" t="n">
+        <v>0.30142</v>
+      </c>
+      <c r="BI125" t="n">
+        <v>0.30992</v>
+      </c>
+      <c r="BJ125" t="n">
+        <v>0.31248</v>
+      </c>
+      <c r="BK125" t="n">
+        <v>0.314</v>
+      </c>
+      <c r="BL125" t="n">
+        <v>0.30952</v>
+      </c>
+      <c r="BM125" t="n">
+        <v>0.2968</v>
+      </c>
+      <c r="BN125" t="n">
+        <v>0.29555</v>
+      </c>
+      <c r="BO125" t="n">
+        <v>0.30009</v>
+      </c>
+      <c r="BP125" t="n">
+        <v>0.30761</v>
+      </c>
+      <c r="BQ125" t="n">
+        <v>0.30666</v>
+      </c>
+      <c r="BR125" t="n">
+        <v>0.28841</v>
+      </c>
+      <c r="BS125" t="n">
+        <v>0.33673</v>
+      </c>
+      <c r="BT125" t="n">
+        <v>0.25357</v>
+      </c>
+      <c r="BU125" t="n">
+        <v>0.3373</v>
+      </c>
+      <c r="BV125" t="n">
+        <v>0.31216</v>
+      </c>
+      <c r="BW125" t="n">
+        <v>0.32592</v>
+      </c>
+      <c r="BX125" t="n">
+        <v>0.32813</v>
+      </c>
+      <c r="BY125" t="n">
+        <v>0.27425</v>
+      </c>
+      <c r="BZ125" t="n">
+        <v>0.33565</v>
+      </c>
+      <c r="CA125" t="n">
+        <v>0.32025</v>
+      </c>
+      <c r="CB125" t="n">
+        <v>0.32871</v>
+      </c>
+      <c r="CC125" t="n">
+        <v>0.30137</v>
+      </c>
+      <c r="CD125" t="n">
+        <v>0.33747</v>
+      </c>
+      <c r="CE125" t="n">
+        <v>0.32801</v>
+      </c>
+      <c r="CF125" t="n">
+        <v>0.36832</v>
+      </c>
+      <c r="CG125" t="n">
+        <v>0.3398</v>
+      </c>
+      <c r="CH125" t="n">
+        <v>0.41055</v>
+      </c>
+      <c r="CI125" t="n">
+        <v>0.2622</v>
+      </c>
+      <c r="CJ125" t="n">
+        <v>0.33204</v>
+      </c>
+      <c r="CK125" t="n">
+        <v>0.42002</v>
+      </c>
+      <c r="CL125" t="n">
+        <v>0.34427</v>
+      </c>
+      <c r="CM125" t="n">
+        <v>0.43954</v>
+      </c>
+      <c r="CN125" t="n">
+        <v>0.32649</v>
+      </c>
+      <c r="CO125" t="n">
+        <v>0.39933</v>
+      </c>
+      <c r="CP125" t="n">
+        <v>0.35115</v>
+      </c>
+      <c r="CQ125" t="n">
+        <v>0.37903</v>
+      </c>
+      <c r="CR125" t="n">
+        <v>0.37673</v>
+      </c>
+      <c r="CS125" t="n">
+        <v>0.53008</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B126" t="n">
+        <v>0.31951</v>
+      </c>
+      <c r="C126" t="n">
+        <v>0.8649199999999999</v>
+      </c>
+      <c r="D126" t="n">
+        <v>1.44335</v>
+      </c>
+      <c r="E126" t="n">
+        <v>1.13747</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0.6856100000000001</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0.7758700000000001</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0.6372899999999999</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0.50136</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0.39815</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0.43946</v>
+      </c>
+      <c r="L126" t="n">
+        <v>0.48938</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0.42979</v>
+      </c>
+      <c r="N126" t="n">
+        <v>0.41509</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0.4045899999999999</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0.40404</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0.40333</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0.46059</v>
+      </c>
+      <c r="S126" t="n">
+        <v>0.40429</v>
+      </c>
+      <c r="T126" t="n">
+        <v>0.42479</v>
+      </c>
+      <c r="U126" t="n">
+        <v>0.38786</v>
+      </c>
+      <c r="V126" t="n">
+        <v>0.42544</v>
+      </c>
+      <c r="W126" t="n">
+        <v>0.38373</v>
+      </c>
+      <c r="X126" t="n">
+        <v>0.39821</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>0.41588</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>0.38783</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>0.41569</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>0.40369</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>0.40432</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>0.40683</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>0.37652</v>
+      </c>
+      <c r="AF126" t="n">
+        <v>0.39244</v>
+      </c>
+      <c r="AG126" t="n">
+        <v>0.39002</v>
+      </c>
+      <c r="AH126" t="n">
+        <v>0.37759</v>
+      </c>
+      <c r="AI126" t="n">
+        <v>0.48609</v>
+      </c>
+      <c r="AJ126" t="n">
+        <v>0.35659</v>
+      </c>
+      <c r="AK126" t="n">
+        <v>0.30552</v>
+      </c>
+      <c r="AL126" t="n">
+        <v>0.28724</v>
+      </c>
+      <c r="AM126" t="n">
+        <v>0.34351</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>0.35554</v>
+      </c>
+      <c r="AO126" t="n">
+        <v>0.30536</v>
+      </c>
+      <c r="AP126" t="n">
+        <v>0.33369</v>
+      </c>
+      <c r="AQ126" t="n">
+        <v>0.3042</v>
+      </c>
+      <c r="AR126" t="n">
+        <v>0.30755</v>
+      </c>
+      <c r="AS126" t="n">
+        <v>0.29891</v>
+      </c>
+      <c r="AT126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU126" t="n">
+        <v>0.5229</v>
+      </c>
+      <c r="AV126" t="n">
+        <v>0.35651</v>
+      </c>
+      <c r="AW126" t="n">
+        <v>0.22296</v>
+      </c>
+      <c r="AX126" t="n">
+        <v>0.24824</v>
+      </c>
+      <c r="AY126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ126" t="n">
+        <v>0.29988</v>
+      </c>
+      <c r="BA126" t="n">
+        <v>0.15554</v>
+      </c>
+      <c r="BB126" t="n">
+        <v>0.274</v>
+      </c>
+      <c r="BC126" t="n">
+        <v>0.2754</v>
+      </c>
+      <c r="BD126" t="n">
+        <v>-0.00902</v>
+      </c>
+      <c r="BE126" t="n">
+        <v>0.33491</v>
+      </c>
+      <c r="BF126" t="n">
+        <v>0.30113</v>
+      </c>
+      <c r="BG126" t="n">
+        <v>0.25974</v>
+      </c>
+      <c r="BH126" t="n">
+        <v>0.25278</v>
+      </c>
+      <c r="BI126" t="n">
+        <v>0.3083</v>
+      </c>
+      <c r="BJ126" t="n">
+        <v>0.28166</v>
+      </c>
+      <c r="BK126" t="n">
+        <v>0.292</v>
+      </c>
+      <c r="BL126" t="n">
+        <v>0.30526</v>
+      </c>
+      <c r="BM126" t="n">
+        <v>0.289</v>
+      </c>
+      <c r="BN126" t="n">
+        <v>0.30421</v>
+      </c>
+      <c r="BO126" t="n">
+        <v>0.31053</v>
+      </c>
+      <c r="BP126" t="n">
+        <v>0.31845</v>
+      </c>
+      <c r="BQ126" t="n">
+        <v>0.31822</v>
+      </c>
+      <c r="BR126" t="n">
+        <v>0.3107799999999999</v>
+      </c>
+      <c r="BS126" t="n">
+        <v>0.32783</v>
+      </c>
+      <c r="BT126" t="n">
+        <v>0.32941</v>
+      </c>
+      <c r="BU126" t="n">
+        <v>0.38669</v>
+      </c>
+      <c r="BV126" t="n">
+        <v>0.38332</v>
+      </c>
+      <c r="BW126" t="n">
+        <v>0.34359</v>
+      </c>
+      <c r="BX126" t="n">
+        <v>0.35221</v>
+      </c>
+      <c r="BY126" t="n">
+        <v>0.33255</v>
+      </c>
+      <c r="BZ126" t="n">
+        <v>0.32083</v>
+      </c>
+      <c r="CA126" t="n">
+        <v>0.35947</v>
+      </c>
+      <c r="CB126" t="n">
+        <v>0.33424</v>
+      </c>
+      <c r="CC126" t="n">
+        <v>0.34374</v>
+      </c>
+      <c r="CD126" t="n">
+        <v>0.35406</v>
+      </c>
+      <c r="CE126" t="n">
+        <v>0.35398</v>
+      </c>
+      <c r="CF126" t="n">
+        <v>0.34092</v>
+      </c>
+      <c r="CG126" t="n">
+        <v>0.5410499999999999</v>
+      </c>
+      <c r="CH126" t="n">
+        <v>0.43133</v>
+      </c>
+      <c r="CI126" t="n">
+        <v>0.78313</v>
+      </c>
+      <c r="CJ126" t="n">
+        <v>0.43253</v>
+      </c>
+      <c r="CK126" t="n">
+        <v>0.4336</v>
+      </c>
+      <c r="CL126" t="n">
+        <v>0.36362</v>
+      </c>
+      <c r="CM126" t="n">
+        <v>0.43984</v>
+      </c>
+      <c r="CN126" t="n">
+        <v>0.36875</v>
+      </c>
+      <c r="CO126" t="n">
+        <v>0.35545</v>
+      </c>
+      <c r="CP126" t="n">
+        <v>0.32421</v>
+      </c>
+      <c r="CQ126" t="n">
+        <v>0.32322</v>
+      </c>
+      <c r="CR126" t="n">
+        <v>0.31973</v>
+      </c>
+      <c r="CS126" t="n">
+        <v>0.30654</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B127" t="n">
+        <v>0.3183</v>
+      </c>
+      <c r="C127" t="n">
+        <v>0.38789</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0.31883</v>
+      </c>
+      <c r="E127" t="n">
+        <v>1.32128</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0.29863</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0.32833</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0.29391</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0.29793</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0.29242</v>
+      </c>
+      <c r="K127" t="n">
+        <v>0.29381</v>
+      </c>
+      <c r="L127" t="n">
+        <v>0.28492</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0.29086</v>
+      </c>
+      <c r="N127" t="n">
+        <v>0.30895</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0.30731</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0.3107799999999999</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>0.30687</v>
+      </c>
+      <c r="R127" t="n">
+        <v>0.28014</v>
+      </c>
+      <c r="S127" t="n">
+        <v>0.28023</v>
+      </c>
+      <c r="T127" t="n">
+        <v>0.30003</v>
+      </c>
+      <c r="U127" t="n">
+        <v>0.31484</v>
+      </c>
+      <c r="V127" t="n">
+        <v>0.30236</v>
+      </c>
+      <c r="W127" t="n">
+        <v>0.23992</v>
+      </c>
+      <c r="X127" t="n">
+        <v>0.28723</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>0.34709</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>0.24414</v>
+      </c>
+      <c r="AA127" t="n">
+        <v>0.31502</v>
+      </c>
+      <c r="AB127" t="n">
+        <v>0.3525</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>0.33101</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>0.32958</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>0.32972</v>
+      </c>
+      <c r="AF127" t="n">
+        <v>0.32655</v>
+      </c>
+      <c r="AG127" t="n">
+        <v>0.31722</v>
+      </c>
+      <c r="AH127" t="n">
+        <v>0.29499</v>
+      </c>
+      <c r="AI127" t="n">
+        <v>0.31161</v>
+      </c>
+      <c r="AJ127" t="n">
+        <v>0.23789</v>
+      </c>
+      <c r="AK127" t="n">
+        <v>0.3222</v>
+      </c>
+      <c r="AL127" t="n">
+        <v>0.27329</v>
+      </c>
+      <c r="AM127" t="n">
+        <v>0.26317</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>0.3196</v>
+      </c>
+      <c r="AO127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP127" t="n">
+        <v>0.38181</v>
+      </c>
+      <c r="AQ127" t="n">
+        <v>0.22967</v>
+      </c>
+      <c r="AR127" t="n">
+        <v>0.26555</v>
+      </c>
+      <c r="AS127" t="n">
+        <v>0.3773</v>
+      </c>
+      <c r="AT127" t="n">
+        <v>0.33961</v>
+      </c>
+      <c r="AU127" t="n">
+        <v>0.42143</v>
+      </c>
+      <c r="AV127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX127" t="n">
+        <v>0.26041</v>
+      </c>
+      <c r="AY127" t="n">
+        <v>0.30505</v>
+      </c>
+      <c r="AZ127" t="n">
+        <v>0.33453</v>
+      </c>
+      <c r="BA127" t="n">
+        <v>0.37915</v>
+      </c>
+      <c r="BB127" t="n">
+        <v>0.29504</v>
+      </c>
+      <c r="BC127" t="n">
+        <v>0.33931</v>
+      </c>
+      <c r="BD127" t="n">
+        <v>0.31916</v>
+      </c>
+      <c r="BE127" t="n">
+        <v>0.31198</v>
+      </c>
+      <c r="BF127" t="n">
+        <v>0.28061</v>
+      </c>
+      <c r="BG127" t="n">
+        <v>0.2761</v>
+      </c>
+      <c r="BH127" t="n">
+        <v>0.34514</v>
+      </c>
+      <c r="BI127" t="n">
+        <v>0.39418</v>
+      </c>
+      <c r="BJ127" t="n">
+        <v>0.28444</v>
+      </c>
+      <c r="BK127" t="n">
+        <v>0.32304</v>
+      </c>
+      <c r="BL127" t="n">
+        <v>0.30348</v>
+      </c>
+      <c r="BM127" t="n">
+        <v>0.34088</v>
+      </c>
+      <c r="BN127" t="n">
+        <v>0.31149</v>
+      </c>
+      <c r="BO127" t="n">
+        <v>0.49749</v>
+      </c>
+      <c r="BP127" t="n">
+        <v>0.36236</v>
+      </c>
+      <c r="BQ127" t="n">
+        <v>0.42432</v>
+      </c>
+      <c r="BR127" t="n">
+        <v>0.31833</v>
+      </c>
+      <c r="BS127" t="n">
+        <v>0.37114</v>
+      </c>
+      <c r="BT127" t="n">
+        <v>0.3627</v>
+      </c>
+      <c r="BU127" t="n">
+        <v>0.45176</v>
+      </c>
+      <c r="BV127" t="n">
+        <v>0.33382</v>
+      </c>
+      <c r="BW127" t="n">
+        <v>0.36301</v>
+      </c>
+      <c r="BX127" t="n">
+        <v>0.33711</v>
+      </c>
+      <c r="BY127" t="n">
+        <v>0.3785</v>
+      </c>
+      <c r="BZ127" t="n">
+        <v>0.34557</v>
+      </c>
+      <c r="CA127" t="n">
+        <v>0.36477</v>
+      </c>
+      <c r="CB127" t="n">
+        <v>0.41558</v>
+      </c>
+      <c r="CC127" t="n">
+        <v>0.37643</v>
+      </c>
+      <c r="CD127" t="n">
+        <v>0.37017</v>
+      </c>
+      <c r="CE127" t="n">
+        <v>0.37769</v>
+      </c>
+      <c r="CF127" t="n">
+        <v>0.37541</v>
+      </c>
+      <c r="CG127" t="n">
+        <v>0.41998</v>
+      </c>
+      <c r="CH127" t="n">
+        <v>0.40768</v>
+      </c>
+      <c r="CI127" t="n">
+        <v>0.40817</v>
+      </c>
+      <c r="CJ127" t="n">
+        <v>0.41224</v>
+      </c>
+      <c r="CK127" t="n">
+        <v>0.43755</v>
+      </c>
+      <c r="CL127" t="n">
+        <v>0.39423</v>
+      </c>
+      <c r="CM127" t="n">
+        <v>0.38237</v>
+      </c>
+      <c r="CN127" t="n">
+        <v>0.39007</v>
+      </c>
+      <c r="CO127" t="n">
+        <v>0.38397</v>
+      </c>
+      <c r="CP127" t="n">
+        <v>0.34273</v>
+      </c>
+      <c r="CQ127" t="n">
+        <v>0.34368</v>
+      </c>
+      <c r="CR127" t="n">
+        <v>0.32592</v>
+      </c>
+      <c r="CS127" t="n">
+        <v>0.33392</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B128" t="n">
+        <v>0.32814</v>
+      </c>
+      <c r="C128" t="n">
+        <v>0.48901</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0.3822</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0.43395</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0.39834</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0.39175</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0.35459</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0.36356</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0.36241</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0.37362</v>
+      </c>
+      <c r="L128" t="n">
+        <v>0.37305</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0.36358</v>
+      </c>
+      <c r="N128" t="n">
+        <v>0.36546</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0.34865</v>
+      </c>
+      <c r="P128" t="n">
+        <v>0.3737799999999999</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>0.35649</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0.36244</v>
+      </c>
+      <c r="S128" t="n">
+        <v>0.33838</v>
+      </c>
+      <c r="T128" t="n">
+        <v>0.33599</v>
+      </c>
+      <c r="U128" t="n">
+        <v>0.34304</v>
+      </c>
+      <c r="V128" t="n">
+        <v>0.33394</v>
+      </c>
+      <c r="W128" t="n">
+        <v>0.33006</v>
+      </c>
+      <c r="X128" t="n">
+        <v>0.33432</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>0.33006</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>0.33926</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>0.41762</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>0.35403</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>0.36305</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>0.34705</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>0.33166</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>0.3296</v>
+      </c>
+      <c r="AG128" t="n">
+        <v>0.33185</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>0.3207</v>
+      </c>
+      <c r="AI128" t="n">
+        <v>0.33312</v>
+      </c>
+      <c r="AJ128" t="n">
+        <v>0.33994</v>
+      </c>
+      <c r="AK128" t="n">
+        <v>0.35448</v>
+      </c>
+      <c r="AL128" t="n">
+        <v>0.29444</v>
+      </c>
+      <c r="AM128" t="n">
+        <v>0.31842</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>0.33157</v>
+      </c>
+      <c r="AO128" t="n">
+        <v>0.32608</v>
+      </c>
+      <c r="AP128" t="n">
+        <v>0.29876</v>
+      </c>
+      <c r="AQ128" t="n">
+        <v>0.30929</v>
+      </c>
+      <c r="AR128" t="n">
+        <v>0.29483</v>
+      </c>
+      <c r="AS128" t="n">
+        <v>0.9901599999999999</v>
+      </c>
+      <c r="AT128" t="n">
+        <v>0.69662</v>
+      </c>
+      <c r="AU128" t="n">
+        <v>0.34632</v>
+      </c>
+      <c r="AV128" t="n">
+        <v>0.37216</v>
+      </c>
+      <c r="AW128" t="n">
+        <v>0.25288</v>
+      </c>
+      <c r="AX128" t="n">
+        <v>0.27967</v>
+      </c>
+      <c r="AY128" t="n">
+        <v>0.30088</v>
+      </c>
+      <c r="AZ128" t="n">
+        <v>0.30132</v>
+      </c>
+      <c r="BA128" t="n">
+        <v>0.31807</v>
+      </c>
+      <c r="BB128" t="n">
+        <v>0.31776</v>
+      </c>
+      <c r="BC128" t="n">
+        <v>0.31871</v>
+      </c>
+      <c r="BD128" t="n">
+        <v>0.36118</v>
+      </c>
+      <c r="BE128" t="n">
+        <v>0.31354</v>
+      </c>
+      <c r="BF128" t="n">
+        <v>0.32318</v>
+      </c>
+      <c r="BG128" t="n">
+        <v>0.29745</v>
+      </c>
+      <c r="BH128" t="n">
+        <v>0.23926</v>
+      </c>
+      <c r="BI128" t="n">
+        <v>0.31274</v>
+      </c>
+      <c r="BJ128" t="n">
+        <v>0.30315</v>
+      </c>
+      <c r="BK128" t="n">
+        <v>0.32015</v>
+      </c>
+      <c r="BL128" t="n">
+        <v>0.46841</v>
+      </c>
+      <c r="BM128" t="n">
+        <v>0.47111</v>
+      </c>
+      <c r="BN128" t="n">
+        <v>0.42176</v>
+      </c>
+      <c r="BO128" t="n">
+        <v>0.5186000000000001</v>
+      </c>
+      <c r="BP128" t="n">
+        <v>0.49211</v>
+      </c>
+      <c r="BQ128" t="n">
+        <v>0.39894</v>
+      </c>
+      <c r="BR128" t="n">
+        <v>0.33389</v>
+      </c>
+      <c r="BS128" t="n">
+        <v>0.69628</v>
+      </c>
+      <c r="BT128" t="n">
+        <v>0.7742899999999999</v>
+      </c>
+      <c r="BU128" t="n">
+        <v>0.37445</v>
+      </c>
+      <c r="BV128" t="n">
+        <v>0.3922</v>
+      </c>
+      <c r="BW128" t="n">
+        <v>0.34158</v>
+      </c>
+      <c r="BX128" t="n">
+        <v>0.3912</v>
+      </c>
+      <c r="BY128" t="n">
+        <v>0.7251599999999999</v>
+      </c>
+      <c r="BZ128" t="n">
+        <v>0.8936499999999999</v>
+      </c>
+      <c r="CA128" t="n">
+        <v>0.65407</v>
+      </c>
+      <c r="CB128" t="n">
+        <v>0.9246599999999999</v>
+      </c>
+      <c r="CC128" t="n">
+        <v>1.09608</v>
+      </c>
+      <c r="CD128" t="n">
+        <v>0.37782</v>
+      </c>
+      <c r="CE128" t="n">
+        <v>0.37175</v>
+      </c>
+      <c r="CF128" t="n">
+        <v>0.40767</v>
+      </c>
+      <c r="CG128" t="n">
+        <v>0.4064</v>
+      </c>
+      <c r="CH128" t="n">
+        <v>0.40177</v>
+      </c>
+      <c r="CI128" t="n">
+        <v>0.62887</v>
+      </c>
+      <c r="CJ128" t="n">
+        <v>0.34074</v>
+      </c>
+      <c r="CK128" t="n">
+        <v>0.34356</v>
+      </c>
+      <c r="CL128" t="n">
+        <v>0.44461</v>
+      </c>
+      <c r="CM128" t="n">
+        <v>0.35865</v>
+      </c>
+      <c r="CN128" t="n">
+        <v>0.40388</v>
+      </c>
+      <c r="CO128" t="n">
+        <v>0.36012</v>
+      </c>
+      <c r="CP128" t="n">
+        <v>0.36513</v>
+      </c>
+      <c r="CQ128" t="n">
+        <v>0.36906</v>
+      </c>
+      <c r="CR128" t="n">
+        <v>0.34005</v>
+      </c>
+      <c r="CS128" t="n">
+        <v>0.3482</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B129" t="n">
+        <v>0.3355</v>
+      </c>
+      <c r="C129" t="n">
+        <v>0.35322</v>
+      </c>
+      <c r="D129" t="n">
+        <v>0.45899</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0.364</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0.47168</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0.36522</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0.34194</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0.35199</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0.3452</v>
+      </c>
+      <c r="K129" t="n">
+        <v>0.33732</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0.3306</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0.33575</v>
+      </c>
+      <c r="N129" t="n">
+        <v>0.33503</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0.33849</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0.3400899999999999</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>0.33736</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0.33277</v>
+      </c>
+      <c r="S129" t="n">
+        <v>0.33148</v>
+      </c>
+      <c r="T129" t="n">
+        <v>0.33629</v>
+      </c>
+      <c r="U129" t="n">
+        <v>0.33175</v>
+      </c>
+      <c r="V129" t="n">
+        <v>0.32829</v>
+      </c>
+      <c r="W129" t="n">
+        <v>0.33307</v>
+      </c>
+      <c r="X129" t="n">
+        <v>0.32884</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>0.33046</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>0.33353</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>0.33807</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>0.36058</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>0.37343</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>0.36834</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>0.36131</v>
+      </c>
+      <c r="AF129" t="n">
+        <v>0.42994</v>
+      </c>
+      <c r="AG129" t="n">
+        <v>0.33209</v>
+      </c>
+      <c r="AH129" t="n">
+        <v>0.81396</v>
+      </c>
+      <c r="AI129" t="n">
+        <v>0.93725</v>
+      </c>
+      <c r="AJ129" t="n">
+        <v>0.929</v>
+      </c>
+      <c r="AK129" t="n">
+        <v>1.44312</v>
+      </c>
+      <c r="AL129" t="n">
+        <v>0.85823</v>
+      </c>
+      <c r="AM129" t="n">
+        <v>1.50557</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>1.18724</v>
+      </c>
+      <c r="AO129" t="n">
+        <v>0.94016</v>
+      </c>
+      <c r="AP129" t="n">
+        <v>0.9244199999999999</v>
+      </c>
+      <c r="AQ129" t="n">
+        <v>1.15627</v>
+      </c>
+      <c r="AR129" t="n">
+        <v>0.8955</v>
+      </c>
+      <c r="AS129" t="n">
+        <v>1.34683</v>
+      </c>
+      <c r="AT129" t="n">
+        <v>1.21602</v>
+      </c>
+      <c r="AU129" t="n">
+        <v>1.24983</v>
+      </c>
+      <c r="AV129" t="n">
+        <v>0.84735</v>
+      </c>
+      <c r="AW129" t="n">
+        <v>1.35243</v>
+      </c>
+      <c r="AX129" t="n">
+        <v>0.4486</v>
+      </c>
+      <c r="AY129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AZ129" t="n">
+        <v>1.53517</v>
+      </c>
+      <c r="BA129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BB129" t="n">
+        <v>0.60336</v>
+      </c>
+      <c r="BC129" t="n">
+        <v>1.33359</v>
+      </c>
+      <c r="BD129" t="n">
+        <v>1.29675</v>
+      </c>
+      <c r="BE129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BF129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BG129" t="n">
+        <v>1.45903</v>
+      </c>
+      <c r="BH129" t="n">
+        <v>1.72781</v>
+      </c>
+      <c r="BI129" t="n">
+        <v>1.58351</v>
+      </c>
+      <c r="BJ129" t="n">
+        <v>1.46785</v>
+      </c>
+      <c r="BK129" t="n">
+        <v>1.59995</v>
+      </c>
+      <c r="BL129" t="n">
+        <v>1.26773</v>
+      </c>
+      <c r="BM129" t="n">
+        <v>1.53708</v>
+      </c>
+      <c r="BN129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BO129" t="n">
+        <v>0.89485</v>
+      </c>
+      <c r="BP129" t="n">
+        <v>1.72059</v>
+      </c>
+      <c r="BQ129" t="n">
+        <v>0.67659</v>
+      </c>
+      <c r="BR129" t="n">
+        <v>1.19199</v>
+      </c>
+      <c r="BS129" t="n">
+        <v>0.68388</v>
+      </c>
+      <c r="BT129" t="n">
+        <v>0.6511</v>
+      </c>
+      <c r="BU129" t="n">
+        <v>0.73964</v>
+      </c>
+      <c r="BV129" t="n">
+        <v>0.66759</v>
+      </c>
+      <c r="BW129" t="n">
+        <v>0.6620900000000001</v>
+      </c>
+      <c r="BX129" t="n">
+        <v>1.17515</v>
+      </c>
+      <c r="BY129" t="n">
+        <v>0.78847</v>
+      </c>
+      <c r="BZ129" t="n">
+        <v>1.4677</v>
+      </c>
+      <c r="CA129" t="n">
+        <v>0.76811</v>
+      </c>
+      <c r="CB129" t="n">
+        <v>0.7500399999999999</v>
+      </c>
+      <c r="CC129" t="n">
+        <v>1.025</v>
+      </c>
+      <c r="CD129" t="n">
+        <v>0.6974900000000001</v>
+      </c>
+      <c r="CE129" t="n">
+        <v>0.65076</v>
+      </c>
+      <c r="CF129" t="n">
+        <v>0.6052999999999999</v>
+      </c>
+      <c r="CG129" t="n">
+        <v>0.51566</v>
+      </c>
+      <c r="CH129" t="n">
+        <v>0.36775</v>
+      </c>
+      <c r="CI129" t="n">
+        <v>0.50304</v>
+      </c>
+      <c r="CJ129" t="n">
+        <v>0.2401</v>
+      </c>
+      <c r="CK129" t="n">
+        <v>0.3689</v>
+      </c>
+      <c r="CL129" t="n">
+        <v>0.3516</v>
+      </c>
+      <c r="CM129" t="n">
+        <v>0.32916</v>
+      </c>
+      <c r="CN129" t="n">
+        <v>0.34551</v>
+      </c>
+      <c r="CO129" t="n">
+        <v>0.33443</v>
+      </c>
+      <c r="CP129" t="n">
+        <v>0.31284</v>
+      </c>
+      <c r="CQ129" t="n">
+        <v>0.33886</v>
+      </c>
+      <c r="CR129" t="n">
+        <v>0.9852300000000001</v>
+      </c>
+      <c r="CS129" t="n">
+        <v>0.30906</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="B130" t="n">
+        <v>0.32001</v>
+      </c>
+      <c r="C130" t="n">
+        <v>0.66587</v>
+      </c>
+      <c r="D130" t="n">
+        <v>0.39645</v>
+      </c>
+      <c r="E130" t="n">
+        <v>0.41355</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0.33692</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0.32179</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0.33387</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0.35081</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0.31245</v>
+      </c>
+      <c r="K130" t="n">
+        <v>0.38145</v>
+      </c>
+      <c r="L130" t="n">
+        <v>0.35817</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0.32881</v>
+      </c>
+      <c r="N130" t="n">
+        <v>0.32293</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0.32246</v>
+      </c>
+      <c r="P130" t="n">
+        <v>0.31686</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>0.31469</v>
+      </c>
+      <c r="R130" t="n">
+        <v>0.36913</v>
+      </c>
+      <c r="S130" t="n">
+        <v>0.32513</v>
+      </c>
+      <c r="T130" t="n">
+        <v>0.29852</v>
+      </c>
+      <c r="U130" t="n">
+        <v>0.2858</v>
+      </c>
+      <c r="V130" t="n">
+        <v>0.30099</v>
+      </c>
+      <c r="W130" t="n">
+        <v>0.31301</v>
+      </c>
+      <c r="X130" t="n">
+        <v>0.31619</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>0.31164</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>0.29825</v>
+      </c>
+      <c r="AA130" t="n">
+        <v>0.3031</v>
+      </c>
+      <c r="AB130" t="n">
+        <v>0.31412</v>
+      </c>
+      <c r="AC130" t="n">
+        <v>0.31644</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>0.30833</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>0.29434</v>
+      </c>
+      <c r="AF130" t="n">
+        <v>0.31874</v>
+      </c>
+      <c r="AG130" t="n">
+        <v>0.30937</v>
+      </c>
+      <c r="AH130" t="n">
+        <v>0.32978</v>
+      </c>
+      <c r="AI130" t="n">
+        <v>0.34886</v>
+      </c>
+      <c r="AJ130" t="n">
+        <v>0.37243</v>
+      </c>
+      <c r="AK130" t="n">
+        <v>0.37099</v>
+      </c>
+      <c r="AL130" t="n">
+        <v>0.32751</v>
+      </c>
+      <c r="AM130" t="n">
+        <v>0.96048</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>0.36308</v>
+      </c>
+      <c r="AO130" t="n">
+        <v>0.34189</v>
+      </c>
+      <c r="AP130" t="n">
+        <v>0.45689</v>
+      </c>
+      <c r="AQ130" t="n">
+        <v>0.34243</v>
+      </c>
+      <c r="AR130" t="n">
+        <v>0.33089</v>
+      </c>
+      <c r="AS130" t="n">
+        <v>0.31525</v>
+      </c>
+      <c r="AT130" t="n">
+        <v>0.33286</v>
+      </c>
+      <c r="AU130" t="n">
+        <v>0.33272</v>
+      </c>
+      <c r="AV130" t="n">
+        <v>0.30937</v>
+      </c>
+      <c r="AW130" t="n">
+        <v>0.32573</v>
+      </c>
+      <c r="AX130" t="n">
+        <v>0.27646</v>
+      </c>
+      <c r="AY130" t="n">
+        <v>0.32436</v>
+      </c>
+      <c r="AZ130" t="n">
+        <v>0.33371</v>
+      </c>
+      <c r="BA130" t="n">
+        <v>0.31233</v>
+      </c>
+      <c r="BB130" t="n">
+        <v>0.31835</v>
+      </c>
+      <c r="BC130" t="n">
+        <v>0.32067</v>
+      </c>
+      <c r="BD130" t="n">
+        <v>0.3273</v>
+      </c>
+      <c r="BE130" t="n">
+        <v>0.33318</v>
+      </c>
+      <c r="BF130" t="n">
+        <v>0.32812</v>
+      </c>
+      <c r="BG130" t="n">
+        <v>0.3167</v>
+      </c>
+      <c r="BH130" t="n">
+        <v>0.30607</v>
+      </c>
+      <c r="BI130" t="n">
+        <v>0.30933</v>
+      </c>
+      <c r="BJ130" t="n">
+        <v>0.31092</v>
+      </c>
+      <c r="BK130" t="n">
+        <v>0.76362</v>
+      </c>
+      <c r="BL130" t="n">
+        <v>0.33679</v>
+      </c>
+      <c r="BM130" t="n">
+        <v>1.06033</v>
+      </c>
+      <c r="BN130" t="n">
+        <v>1.31634</v>
+      </c>
+      <c r="BO130" t="n">
+        <v>0.99025</v>
+      </c>
+      <c r="BP130" t="n">
+        <v>0.49448</v>
+      </c>
+      <c r="BQ130" t="n">
+        <v>0.33051</v>
+      </c>
+      <c r="BR130" t="n">
+        <v>0.35346</v>
+      </c>
+      <c r="BS130" t="n">
+        <v>0.36487</v>
+      </c>
+      <c r="BT130" t="n">
+        <v>0.34161</v>
+      </c>
+      <c r="BU130" t="n">
+        <v>0.33914</v>
+      </c>
+      <c r="BV130" t="n">
+        <v>0.3385</v>
+      </c>
+      <c r="BW130" t="n">
+        <v>0.76767</v>
+      </c>
+      <c r="BX130" t="n">
+        <v>0.36832</v>
+      </c>
+      <c r="BY130" t="n">
+        <v>0.7616900000000001</v>
+      </c>
+      <c r="BZ130" t="n">
+        <v>0.33822</v>
+      </c>
+      <c r="CA130" t="n">
+        <v>0.35126</v>
+      </c>
+      <c r="CB130" t="n">
+        <v>0.35703</v>
+      </c>
+      <c r="CC130" t="n">
+        <v>0.34894</v>
+      </c>
+      <c r="CD130" t="n">
+        <v>0.34124</v>
+      </c>
+      <c r="CE130" t="n">
+        <v>0.35013</v>
+      </c>
+      <c r="CF130" t="n">
+        <v>0.34823</v>
+      </c>
+      <c r="CG130" t="n">
+        <v>0.35308</v>
+      </c>
+      <c r="CH130" t="n">
+        <v>0.35935</v>
+      </c>
+      <c r="CI130" t="n">
+        <v>0.36355</v>
+      </c>
+      <c r="CJ130" t="n">
+        <v>0.36455</v>
+      </c>
+      <c r="CK130" t="n">
+        <v>0.36143</v>
+      </c>
+      <c r="CL130" t="n">
+        <v>0.34772</v>
+      </c>
+      <c r="CM130" t="n">
+        <v>0.35649</v>
+      </c>
+      <c r="CN130" t="n">
+        <v>0.35773</v>
+      </c>
+      <c r="CO130" t="n">
+        <v>0.32445</v>
+      </c>
+      <c r="CP130" t="n">
+        <v>0.30652</v>
+      </c>
+      <c r="CQ130" t="n">
+        <v>0.34313</v>
+      </c>
+      <c r="CR130" t="n">
+        <v>0.32294</v>
+      </c>
+      <c r="CS130" t="n">
+        <v>0.34273</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B131" t="n">
+        <v>0.32876</v>
+      </c>
+      <c r="C131" t="n">
+        <v>0.34352</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0.34251</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0.3435299999999999</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0.34449</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0.34396</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0.34316</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0.33366</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0.34252</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0.33937</v>
+      </c>
+      <c r="L131" t="n">
+        <v>0.27333</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0.34015</v>
+      </c>
+      <c r="N131" t="n">
+        <v>0.33432</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0.33477</v>
+      </c>
+      <c r="P131" t="n">
+        <v>0.32247</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>0.3327</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0.33316</v>
+      </c>
+      <c r="S131" t="n">
+        <v>0.3272</v>
+      </c>
+      <c r="T131" t="n">
+        <v>0.34949</v>
+      </c>
+      <c r="U131" t="n">
+        <v>0.3175</v>
+      </c>
+      <c r="V131" t="n">
+        <v>0.3256</v>
+      </c>
+      <c r="W131" t="n">
+        <v>0.3326</v>
+      </c>
+      <c r="X131" t="n">
+        <v>0.33434</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>0.32486</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>0.32432</v>
+      </c>
+      <c r="AA131" t="n">
+        <v>0.33816</v>
+      </c>
+      <c r="AB131" t="n">
+        <v>0.324</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>0.33574</v>
+      </c>
+      <c r="AD131" t="n">
+        <v>0.33562</v>
+      </c>
+      <c r="AE131" t="n">
+        <v>0.32943</v>
+      </c>
+      <c r="AF131" t="n">
+        <v>0.3264</v>
+      </c>
+      <c r="AG131" t="n">
+        <v>0.31586</v>
+      </c>
+      <c r="AH131" t="n">
+        <v>0.33373</v>
+      </c>
+      <c r="AI131" t="n">
+        <v>0.32951</v>
+      </c>
+      <c r="AJ131" t="n">
+        <v>0.31849</v>
+      </c>
+      <c r="AK131" t="n">
+        <v>0.32468</v>
+      </c>
+      <c r="AL131" t="n">
+        <v>0.29992</v>
+      </c>
+      <c r="AM131" t="n">
+        <v>0.31837</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>0.32175</v>
+      </c>
+      <c r="AO131" t="n">
+        <v>0.32431</v>
+      </c>
+      <c r="AP131" t="n">
+        <v>0.32294</v>
+      </c>
+      <c r="AQ131" t="n">
+        <v>0.31445</v>
+      </c>
+      <c r="AR131" t="n">
+        <v>0.32326</v>
+      </c>
+      <c r="AS131" t="n">
+        <v>0.31467</v>
+      </c>
+      <c r="AT131" t="n">
+        <v>0.31562</v>
+      </c>
+      <c r="AU131" t="n">
+        <v>0.32347</v>
+      </c>
+      <c r="AV131" t="n">
+        <v>0.3208</v>
+      </c>
+      <c r="AW131" t="n">
+        <v>0.32854</v>
+      </c>
+      <c r="AX131" t="n">
+        <v>0.31748</v>
+      </c>
+      <c r="AY131" t="n">
+        <v>0.36963</v>
+      </c>
+      <c r="AZ131" t="n">
+        <v>0.33588</v>
+      </c>
+      <c r="BA131" t="n">
+        <v>0.31916</v>
+      </c>
+      <c r="BB131" t="n">
+        <v>0.6920599999999999</v>
+      </c>
+      <c r="BC131" t="n">
+        <v>1.18825</v>
+      </c>
+      <c r="BD131" t="n">
+        <v>0.40793</v>
+      </c>
+      <c r="BE131" t="n">
+        <v>0.5197000000000001</v>
+      </c>
+      <c r="BF131" t="n">
+        <v>0.4125</v>
+      </c>
+      <c r="BG131" t="n">
+        <v>0.37954</v>
+      </c>
+      <c r="BH131" t="n">
+        <v>0.4038</v>
+      </c>
+      <c r="BI131" t="n">
+        <v>0.47469</v>
+      </c>
+      <c r="BJ131" t="n">
+        <v>0.34113</v>
+      </c>
+      <c r="BK131" t="n">
+        <v>0.36012</v>
+      </c>
+      <c r="BL131" t="n">
+        <v>0.33332</v>
+      </c>
+      <c r="BM131" t="n">
+        <v>0.349</v>
+      </c>
+      <c r="BN131" t="n">
+        <v>0.35012</v>
+      </c>
+      <c r="BO131" t="n">
+        <v>0.5568</v>
+      </c>
+      <c r="BP131" t="n">
+        <v>0.37845</v>
+      </c>
+      <c r="BQ131" t="n">
+        <v>0.34686</v>
+      </c>
+      <c r="BR131" t="n">
+        <v>0.35274</v>
+      </c>
+      <c r="BS131" t="n">
+        <v>0.40757</v>
+      </c>
+      <c r="BT131" t="n">
+        <v>0.34429</v>
+      </c>
+      <c r="BU131" t="n">
+        <v>0.37936</v>
+      </c>
+      <c r="BV131" t="n">
+        <v>0.42485</v>
+      </c>
+      <c r="BW131" t="n">
+        <v>0.34885</v>
+      </c>
+      <c r="BX131" t="n">
+        <v>0.35188</v>
+      </c>
+      <c r="BY131" t="n">
+        <v>0.39638</v>
+      </c>
+      <c r="BZ131" t="n">
+        <v>0.34183</v>
+      </c>
+      <c r="CA131" t="n">
+        <v>0.36971</v>
+      </c>
+      <c r="CB131" t="n">
+        <v>0.47343</v>
+      </c>
+      <c r="CC131" t="n">
+        <v>0.41235</v>
+      </c>
+      <c r="CD131" t="n">
+        <v>0.37081</v>
+      </c>
+      <c r="CE131" t="n">
+        <v>0.40402</v>
+      </c>
+      <c r="CF131" t="n">
+        <v>0.58099</v>
+      </c>
+      <c r="CG131" t="n">
+        <v>0.37269</v>
+      </c>
+      <c r="CH131" t="n">
+        <v>0.36892</v>
+      </c>
+      <c r="CI131" t="n">
+        <v>0.65035</v>
+      </c>
+      <c r="CJ131" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CK131" t="n">
+        <v>0.42671</v>
+      </c>
+      <c r="CL131" t="n">
+        <v>0.59533</v>
+      </c>
+      <c r="CM131" t="n">
+        <v>0.5784</v>
+      </c>
+      <c r="CN131" t="n">
+        <v>0.82167</v>
+      </c>
+      <c r="CO131" t="n">
+        <v>0.34349</v>
+      </c>
+      <c r="CP131" t="n">
+        <v>0.6680499999999999</v>
+      </c>
+      <c r="CQ131" t="n">
+        <v>0.35237</v>
+      </c>
+      <c r="CR131" t="n">
+        <v>0.33279</v>
+      </c>
+      <c r="CS131" t="n">
+        <v>0.33355</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="B132" t="n">
+        <v>0.32209</v>
+      </c>
+      <c r="C132" t="n">
+        <v>0.40419</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0.36933</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0.35975</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0.35508</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0.35223</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0.35189</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0.35506</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0.35115</v>
+      </c>
+      <c r="K132" t="n">
+        <v>0.34983</v>
+      </c>
+      <c r="L132" t="n">
+        <v>0.35201</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0.34587</v>
+      </c>
+      <c r="N132" t="n">
+        <v>0.35302</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0.34917</v>
+      </c>
+      <c r="P132" t="n">
+        <v>0.34916</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>0.34512</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0.34814</v>
+      </c>
+      <c r="S132" t="n">
+        <v>0.35252</v>
+      </c>
+      <c r="T132" t="n">
+        <v>0.35284</v>
+      </c>
+      <c r="U132" t="n">
+        <v>0.34073</v>
+      </c>
+      <c r="V132" t="n">
+        <v>0.35062</v>
+      </c>
+      <c r="W132" t="n">
+        <v>0.35181</v>
+      </c>
+      <c r="X132" t="n">
+        <v>0.34955</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>0.35311</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>0.35311</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>0.36273</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>0.35892</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>0.37292</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>0.3496</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>0.34952</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>0.34422</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>0.34491</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>0.35096</v>
+      </c>
+      <c r="AI132" t="n">
+        <v>0.34243</v>
+      </c>
+      <c r="AJ132" t="n">
+        <v>0.32488</v>
+      </c>
+      <c r="AK132" t="n">
+        <v>1.1978</v>
+      </c>
+      <c r="AL132" t="n">
+        <v>0.44465</v>
+      </c>
+      <c r="AM132" t="n">
+        <v>0.74579</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>0.51034</v>
+      </c>
+      <c r="AO132" t="n">
+        <v>0.7642599999999999</v>
+      </c>
+      <c r="AP132" t="n">
+        <v>0.43548</v>
+      </c>
+      <c r="AQ132" t="n">
+        <v>0.59437</v>
+      </c>
+      <c r="AR132" t="n">
+        <v>0.33325</v>
+      </c>
+      <c r="AS132" t="n">
+        <v>0.31507</v>
+      </c>
+      <c r="AT132" t="n">
+        <v>0.8344</v>
+      </c>
+      <c r="AU132" t="n">
+        <v>0.36004</v>
+      </c>
+      <c r="AV132" t="n">
+        <v>0.3785</v>
+      </c>
+      <c r="AW132" t="n">
+        <v>0.2983</v>
+      </c>
+      <c r="AX132" t="n">
+        <v>0.28243</v>
+      </c>
+      <c r="AY132" t="n">
+        <v>0.32042</v>
+      </c>
+      <c r="AZ132" t="n">
+        <v>0.29394</v>
+      </c>
+      <c r="BA132" t="n">
+        <v>0.28695</v>
+      </c>
+      <c r="BB132" t="n">
+        <v>0.3052</v>
+      </c>
+      <c r="BC132" t="n">
+        <v>0.33371</v>
+      </c>
+      <c r="BD132" t="n">
+        <v>0.34367</v>
+      </c>
+      <c r="BE132" t="n">
+        <v>0.6160399999999999</v>
+      </c>
+      <c r="BF132" t="n">
+        <v>0.37097</v>
+      </c>
+      <c r="BG132" t="n">
+        <v>0.34151</v>
+      </c>
+      <c r="BH132" t="n">
+        <v>0.33718</v>
+      </c>
+      <c r="BI132" t="n">
+        <v>0.40744</v>
+      </c>
+      <c r="BJ132" t="n">
+        <v>0.34122</v>
+      </c>
+      <c r="BK132" t="n">
+        <v>0.6559199999999999</v>
+      </c>
+      <c r="BL132" t="n">
+        <v>0.51923</v>
+      </c>
+      <c r="BM132" t="n">
+        <v>0.78152</v>
+      </c>
+      <c r="BN132" t="n">
+        <v>0.68099</v>
+      </c>
+      <c r="BO132" t="n">
+        <v>1.12373</v>
+      </c>
+      <c r="BP132" t="n">
+        <v>0.64286</v>
+      </c>
+      <c r="BQ132" t="n">
+        <v>0.62038</v>
+      </c>
+      <c r="BR132" t="n">
+        <v>0.34495</v>
+      </c>
+      <c r="BS132" t="n">
+        <v>0.8389</v>
+      </c>
+      <c r="BT132" t="n">
+        <v>0.6496799999999999</v>
+      </c>
+      <c r="BU132" t="n">
+        <v>0.82856</v>
+      </c>
+      <c r="BV132" t="n">
+        <v>0.35426</v>
+      </c>
+      <c r="BW132" t="n">
+        <v>1.17282</v>
+      </c>
+      <c r="BX132" t="n">
+        <v>1.16836</v>
+      </c>
+      <c r="BY132" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BZ132" t="n">
+        <v>1.19977</v>
+      </c>
+      <c r="CA132" t="n">
+        <v>0.95138</v>
+      </c>
+      <c r="CB132" t="n">
+        <v>0.90922</v>
+      </c>
+      <c r="CC132" t="n">
+        <v>1.23724</v>
+      </c>
+      <c r="CD132" t="n">
+        <v>0.8008200000000001</v>
+      </c>
+      <c r="CE132" t="n">
+        <v>1.03646</v>
+      </c>
+      <c r="CF132" t="n">
+        <v>0.81075</v>
+      </c>
+      <c r="CG132" t="n">
+        <v>1.62257</v>
+      </c>
+      <c r="CH132" t="n">
+        <v>1.79862</v>
+      </c>
+      <c r="CI132" t="n">
+        <v>0.79604</v>
+      </c>
+      <c r="CJ132" t="n">
+        <v>0.70731</v>
+      </c>
+      <c r="CK132" t="n">
+        <v>1.2214</v>
+      </c>
+      <c r="CL132" t="n">
+        <v>1.1509</v>
+      </c>
+      <c r="CM132" t="n">
+        <v>0.68759</v>
+      </c>
+      <c r="CN132" t="n">
+        <v>0.40496</v>
+      </c>
+      <c r="CO132" t="n">
+        <v>0.39606</v>
+      </c>
+      <c r="CP132" t="n">
+        <v>0.36541</v>
+      </c>
+      <c r="CQ132" t="n">
+        <v>0.36808</v>
+      </c>
+      <c r="CR132" t="n">
+        <v>0.35586</v>
+      </c>
+      <c r="CS132" t="n">
+        <v>0.34977</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B133" t="n">
+        <v>0.34577</v>
+      </c>
+      <c r="C133" t="n">
+        <v>0.45259</v>
+      </c>
+      <c r="D133" t="n">
+        <v>0.52419</v>
+      </c>
+      <c r="E133" t="n">
+        <v>0.47182</v>
+      </c>
+      <c r="F133" t="n">
+        <v>0.61186</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0.39447</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0.39458</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0.3836</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0.38834</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0.38792</v>
+      </c>
+      <c r="L133" t="n">
+        <v>0.39391</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0.38075</v>
+      </c>
+      <c r="N133" t="n">
+        <v>0.38769</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0.39266</v>
+      </c>
+      <c r="P133" t="n">
+        <v>0.39088</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>0.37874</v>
+      </c>
+      <c r="R133" t="n">
+        <v>0.38099</v>
+      </c>
+      <c r="S133" t="n">
+        <v>0.39388</v>
+      </c>
+      <c r="T133" t="n">
+        <v>0.36984</v>
+      </c>
+      <c r="U133" t="n">
+        <v>0.39226</v>
+      </c>
+      <c r="V133" t="n">
+        <v>0.37169</v>
+      </c>
+      <c r="W133" t="n">
+        <v>0.37408</v>
+      </c>
+      <c r="X133" t="n">
+        <v>0.37777</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>0.38913</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>0.3756</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>0.41168</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>0.4141</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>0.49946</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>0.45649</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>0.41864</v>
+      </c>
+      <c r="AF133" t="n">
+        <v>0.45389</v>
+      </c>
+      <c r="AG133" t="n">
+        <v>0.41721</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>0.57435</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>1.14754</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>0.83813</v>
+      </c>
+      <c r="AK133" t="n">
+        <v>1.19479</v>
+      </c>
+      <c r="AL133" t="n">
+        <v>1.23141</v>
+      </c>
+      <c r="AM133" t="n">
+        <v>1.56657</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>1.31103</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>0.42755</v>
+      </c>
+      <c r="AP133" t="n">
+        <v>0.36409</v>
+      </c>
+      <c r="AQ133" t="n">
+        <v>0.34798</v>
+      </c>
+      <c r="AR133" t="n">
+        <v>0.35583</v>
+      </c>
+      <c r="AS133" t="n">
+        <v>0.6714600000000001</v>
+      </c>
+      <c r="AT133" t="n">
+        <v>0.67345</v>
+      </c>
+      <c r="AU133" t="n">
+        <v>0.69613</v>
+      </c>
+      <c r="AV133" t="n">
+        <v>1.09934</v>
+      </c>
+      <c r="AW133" t="n">
+        <v>0.84658</v>
+      </c>
+      <c r="AX133" t="n">
+        <v>0.58688</v>
+      </c>
+      <c r="AY133" t="n">
+        <v>0.6182300000000001</v>
+      </c>
+      <c r="AZ133" t="n">
+        <v>0.60934</v>
+      </c>
+      <c r="BA133" t="n">
+        <v>0.6887300000000001</v>
+      </c>
+      <c r="BB133" t="n">
+        <v>0.93777</v>
+      </c>
+      <c r="BC133" t="n">
+        <v>0.95043</v>
+      </c>
+      <c r="BD133" t="n">
+        <v>1.28249</v>
+      </c>
+      <c r="BE133" t="n">
+        <v>0.66218</v>
+      </c>
+      <c r="BF133" t="n">
+        <v>0.66673</v>
+      </c>
+      <c r="BG133" t="n">
+        <v>0.6556900000000001</v>
+      </c>
+      <c r="BH133" t="n">
+        <v>0.65271</v>
+      </c>
+      <c r="BI133" t="n">
+        <v>1.19408</v>
+      </c>
+      <c r="BJ133" t="n">
+        <v>0.33923</v>
+      </c>
+      <c r="BK133" t="n">
+        <v>0.31534</v>
+      </c>
+      <c r="BL133" t="n">
+        <v>0.3342</v>
+      </c>
+      <c r="BM133" t="n">
+        <v>0.34937</v>
+      </c>
+      <c r="BN133" t="n">
+        <v>0.33757</v>
+      </c>
+      <c r="BO133" t="n">
+        <v>0.35665</v>
+      </c>
+      <c r="BP133" t="n">
+        <v>0.35166</v>
+      </c>
+      <c r="BQ133" t="n">
+        <v>0.35425</v>
+      </c>
+      <c r="BR133" t="n">
+        <v>0.35946</v>
+      </c>
+      <c r="BS133" t="n">
+        <v>0.37019</v>
+      </c>
+      <c r="BT133" t="n">
+        <v>0.34469</v>
+      </c>
+      <c r="BU133" t="n">
+        <v>0.36329</v>
+      </c>
+      <c r="BV133" t="n">
+        <v>0.33168</v>
+      </c>
+      <c r="BW133" t="n">
+        <v>0.39139</v>
+      </c>
+      <c r="BX133" t="n">
+        <v>0.41094</v>
+      </c>
+      <c r="BY133" t="n">
+        <v>0.45524</v>
+      </c>
+      <c r="BZ133" t="n">
+        <v>0.41798</v>
+      </c>
+      <c r="CA133" t="n">
+        <v>0.46845</v>
+      </c>
+      <c r="CB133" t="n">
+        <v>0.46865</v>
+      </c>
+      <c r="CC133" t="n">
+        <v>0.50082</v>
+      </c>
+      <c r="CD133" t="n">
+        <v>0.6153</v>
+      </c>
+      <c r="CE133" t="n">
+        <v>0.72051</v>
+      </c>
+      <c r="CF133" t="n">
+        <v>0.80844</v>
+      </c>
+      <c r="CG133" t="n">
+        <v>0.57963</v>
+      </c>
+      <c r="CH133" t="n">
+        <v>0.7038099999999999</v>
+      </c>
+      <c r="CI133" t="n">
+        <v>0.87718</v>
+      </c>
+      <c r="CJ133" t="n">
+        <v>1.00342</v>
+      </c>
+      <c r="CK133" t="n">
+        <v>0.72381</v>
+      </c>
+      <c r="CL133" t="n">
+        <v>0.76466</v>
+      </c>
+      <c r="CM133" t="n">
+        <v>0.61739</v>
+      </c>
+      <c r="CN133" t="n">
+        <v>0.6656599999999999</v>
+      </c>
+      <c r="CO133" t="n">
+        <v>1.08778</v>
+      </c>
+      <c r="CP133" t="n">
+        <v>0.7606499999999999</v>
+      </c>
+      <c r="CQ133" t="n">
+        <v>0.44522</v>
+      </c>
+      <c r="CR133" t="n">
+        <v>0.44174</v>
+      </c>
+      <c r="CS133" t="n">
+        <v>0.43494</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B134" t="n">
+        <v>0.3957</v>
+      </c>
+      <c r="C134" t="n">
+        <v>0.50162</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0.4038</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0.4144</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0.42463</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0.42758</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0.4175</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0.41616</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0.40924</v>
+      </c>
+      <c r="K134" t="n">
+        <v>0.37985</v>
+      </c>
+      <c r="L134" t="n">
+        <v>0.413</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0.37286</v>
+      </c>
+      <c r="N134" t="n">
+        <v>0.37931</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0.4566</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0.36831</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>0.36335</v>
+      </c>
+      <c r="R134" t="n">
+        <v>0.3575</v>
+      </c>
+      <c r="S134" t="n">
+        <v>0.35327</v>
+      </c>
+      <c r="T134" t="n">
+        <v>0.35007</v>
+      </c>
+      <c r="U134" t="n">
+        <v>0.35905</v>
+      </c>
+      <c r="V134" t="n">
+        <v>0.29021</v>
+      </c>
+      <c r="W134" t="n">
+        <v>0.34943</v>
+      </c>
+      <c r="X134" t="n">
+        <v>0.34276</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>0.35295</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>0.35905</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>0.36116</v>
+      </c>
+      <c r="AB134" t="n">
+        <v>0.36579</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>0.37262</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>0.34926</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>0.35448</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>0.34825</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>0.37257</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>0.39503</v>
+      </c>
+      <c r="AI134" t="n">
+        <v>0.35814</v>
+      </c>
+      <c r="AJ134" t="n">
+        <v>0.38107</v>
+      </c>
+      <c r="AK134" t="n">
+        <v>0.39237</v>
+      </c>
+      <c r="AL134" t="n">
+        <v>0.37852</v>
+      </c>
+      <c r="AM134" t="n">
+        <v>0.3797</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>0.35138</v>
+      </c>
+      <c r="AO134" t="n">
+        <v>0.35944</v>
+      </c>
+      <c r="AP134" t="n">
+        <v>0.3393</v>
+      </c>
+      <c r="AQ134" t="n">
+        <v>0.33414</v>
+      </c>
+      <c r="AR134" t="n">
+        <v>0.34138</v>
+      </c>
+      <c r="AS134" t="n">
+        <v>0.36895</v>
+      </c>
+      <c r="AT134" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AU134" t="n">
+        <v>0.66803</v>
+      </c>
+      <c r="AV134" t="n">
+        <v>0.63946</v>
+      </c>
+      <c r="AW134" t="n">
+        <v>0.63432</v>
+      </c>
+      <c r="AX134" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AY134" t="n">
+        <v>0.65559</v>
+      </c>
+      <c r="AZ134" t="n">
+        <v>0.6446499999999999</v>
+      </c>
+      <c r="BA134" t="n">
+        <v>0.94733</v>
+      </c>
+      <c r="BB134" t="n">
+        <v>0.6566000000000001</v>
+      </c>
+      <c r="BC134" t="n">
+        <v>0.73391</v>
+      </c>
+      <c r="BD134" t="n">
+        <v>0.6932</v>
+      </c>
+      <c r="BE134" t="n">
+        <v>0.74397</v>
+      </c>
+      <c r="BF134" t="n">
+        <v>1.77229</v>
+      </c>
+      <c r="BG134" t="n">
+        <v>0.36833</v>
+      </c>
+      <c r="BH134" t="n">
+        <v>0.15816</v>
+      </c>
+      <c r="BI134" t="n">
+        <v>0.22098</v>
+      </c>
+      <c r="BJ134" t="n">
+        <v>0.30181</v>
+      </c>
+      <c r="BK134" t="n">
+        <v>0.29946</v>
+      </c>
+      <c r="BL134" t="n">
+        <v>0.32198</v>
+      </c>
+      <c r="BM134" t="n">
+        <v>0.34356</v>
+      </c>
+      <c r="BN134" t="n">
+        <v>0.33587</v>
+      </c>
+      <c r="BO134" t="n">
+        <v>0.33808</v>
+      </c>
+      <c r="BP134" t="n">
+        <v>0.33881</v>
+      </c>
+      <c r="BQ134" t="n">
+        <v>0.35684</v>
+      </c>
+      <c r="BR134" t="n">
+        <v>0.37802</v>
+      </c>
+      <c r="BS134" t="n">
+        <v>0.37787</v>
+      </c>
+      <c r="BT134" t="n">
+        <v>0.66486</v>
+      </c>
+      <c r="BU134" t="n">
+        <v>0.47679</v>
+      </c>
+      <c r="BV134" t="n">
+        <v>0.33496</v>
+      </c>
+      <c r="BW134" t="n">
+        <v>0.42406</v>
+      </c>
+      <c r="BX134" t="n">
+        <v>0.41056</v>
+      </c>
+      <c r="BY134" t="n">
+        <v>0.42273</v>
+      </c>
+      <c r="BZ134" t="n">
+        <v>0.40121</v>
+      </c>
+      <c r="CA134" t="n">
+        <v>0.39171</v>
+      </c>
+      <c r="CB134" t="n">
+        <v>0.34743</v>
+      </c>
+      <c r="CC134" t="n">
+        <v>0.35066</v>
+      </c>
+      <c r="CD134" t="n">
+        <v>0.36932</v>
+      </c>
+      <c r="CE134" t="n">
+        <v>0.37773</v>
+      </c>
+      <c r="CF134" t="n">
+        <v>0.32511</v>
+      </c>
+      <c r="CG134" t="n">
+        <v>0.33742</v>
+      </c>
+      <c r="CH134" t="n">
+        <v>0.36875</v>
+      </c>
+      <c r="CI134" t="n">
+        <v>0.36831</v>
+      </c>
+      <c r="CJ134" t="n">
+        <v>0.35325</v>
+      </c>
+      <c r="CK134" t="n">
+        <v>0.35958</v>
+      </c>
+      <c r="CL134" t="n">
+        <v>0.35483</v>
+      </c>
+      <c r="CM134" t="n">
+        <v>0.37379</v>
+      </c>
+      <c r="CN134" t="n">
+        <v>0.33482</v>
+      </c>
+      <c r="CO134" t="n">
+        <v>0.35643</v>
+      </c>
+      <c r="CP134" t="n">
+        <v>0.31436</v>
+      </c>
+      <c r="CQ134" t="n">
+        <v>0.34804</v>
+      </c>
+      <c r="CR134" t="n">
+        <v>0.33474</v>
+      </c>
+      <c r="CS134" t="n">
+        <v>0.32923</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="B135" t="n">
+        <v>0.29672</v>
+      </c>
+      <c r="C135" t="n">
+        <v>0.45635</v>
+      </c>
+      <c r="D135" t="n">
+        <v>1.18071</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0.37233</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0.35612</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0.97892</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0.34269</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0.30856</v>
+      </c>
+      <c r="J135" t="n">
+        <v>0.29167</v>
+      </c>
+      <c r="K135" t="n">
+        <v>0.3347</v>
+      </c>
+      <c r="L135" t="n">
+        <v>0.27567</v>
+      </c>
+      <c r="M135" t="n">
+        <v>0.27315</v>
+      </c>
+      <c r="N135" t="n">
+        <v>0.3085</v>
+      </c>
+      <c r="O135" t="n">
+        <v>0.27353</v>
+      </c>
+      <c r="P135" t="n">
+        <v>0.31289</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>0.34455</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0.30759</v>
+      </c>
+      <c r="S135" t="n">
+        <v>0.26107</v>
+      </c>
+      <c r="T135" t="n">
+        <v>0.29146</v>
+      </c>
+      <c r="U135" t="n">
+        <v>0.29918</v>
+      </c>
+      <c r="V135" t="n">
+        <v>0.30736</v>
+      </c>
+      <c r="W135" t="n">
+        <v>0.29505</v>
+      </c>
+      <c r="X135" t="n">
+        <v>0.29953</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>0.30401</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>0.2536</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>0.30849</v>
+      </c>
+      <c r="AB135" t="n">
+        <v>0.25268</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>0.24698</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>0.32644</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>0.28688</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>0.27948</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>0.30743</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>0.24222</v>
+      </c>
+      <c r="AI135" t="n">
+        <v>0.3429</v>
+      </c>
+      <c r="AJ135" t="n">
+        <v>0.30836</v>
+      </c>
+      <c r="AK135" t="n">
+        <v>0.30688</v>
+      </c>
+      <c r="AL135" t="n">
+        <v>0.30219</v>
+      </c>
+      <c r="AM135" t="n">
+        <v>0.18496</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>0.28225</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>0.24702</v>
+      </c>
+      <c r="AP135" t="n">
+        <v>0.27175</v>
+      </c>
+      <c r="AQ135" t="n">
+        <v>0.26338</v>
+      </c>
+      <c r="AR135" t="n">
+        <v>0.25949</v>
+      </c>
+      <c r="AS135" t="n">
+        <v>0.094</v>
+      </c>
+      <c r="AT135" t="n">
+        <v>0.31706</v>
+      </c>
+      <c r="AU135" t="n">
+        <v>0.30808</v>
+      </c>
+      <c r="AV135" t="n">
+        <v>0.27062</v>
+      </c>
+      <c r="AW135" t="n">
+        <v>0.25793</v>
+      </c>
+      <c r="AX135" t="n">
+        <v>0.03357</v>
+      </c>
+      <c r="AY135" t="n">
+        <v>0.28942</v>
+      </c>
+      <c r="AZ135" t="n">
+        <v>0.28189</v>
+      </c>
+      <c r="BA135" t="n">
+        <v>0.19732</v>
+      </c>
+      <c r="BB135" t="n">
+        <v>0.31977</v>
+      </c>
+      <c r="BC135" t="n">
+        <v>0.31094</v>
+      </c>
+      <c r="BD135" t="n">
+        <v>0.31274</v>
+      </c>
+      <c r="BE135" t="n">
+        <v>0.30749</v>
+      </c>
+      <c r="BF135" t="n">
+        <v>0.25085</v>
+      </c>
+      <c r="BG135" t="n">
+        <v>0.26991</v>
+      </c>
+      <c r="BH135" t="n">
+        <v>0.25799</v>
+      </c>
+      <c r="BI135" t="n">
+        <v>0.241</v>
+      </c>
+      <c r="BJ135" t="n">
+        <v>0.27628</v>
+      </c>
+      <c r="BK135" t="n">
+        <v>0.28492</v>
+      </c>
+      <c r="BL135" t="n">
+        <v>0.27456</v>
+      </c>
+      <c r="BM135" t="n">
+        <v>0.32184</v>
+      </c>
+      <c r="BN135" t="n">
+        <v>0.32362</v>
+      </c>
+      <c r="BO135" t="n">
+        <v>0.31652</v>
+      </c>
+      <c r="BP135" t="n">
+        <v>0.33911</v>
+      </c>
+      <c r="BQ135" t="n">
+        <v>0.33639</v>
+      </c>
+      <c r="BR135" t="n">
+        <v>0.34572</v>
+      </c>
+      <c r="BS135" t="n">
+        <v>0.36236</v>
+      </c>
+      <c r="BT135" t="n">
+        <v>0.34132</v>
+      </c>
+      <c r="BU135" t="n">
+        <v>0.37613</v>
+      </c>
+      <c r="BV135" t="n">
+        <v>0.38671</v>
+      </c>
+      <c r="BW135" t="n">
+        <v>0.40237</v>
+      </c>
+      <c r="BX135" t="n">
+        <v>0.3773</v>
+      </c>
+      <c r="BY135" t="n">
+        <v>0.52198</v>
+      </c>
+      <c r="BZ135" t="n">
+        <v>0.30234</v>
+      </c>
+      <c r="CA135" t="n">
+        <v>0.35069</v>
+      </c>
+      <c r="CB135" t="n">
+        <v>0.33866</v>
+      </c>
+      <c r="CC135" t="n">
+        <v>0.35301</v>
+      </c>
+      <c r="CD135" t="n">
+        <v>0.33192</v>
+      </c>
+      <c r="CE135" t="n">
+        <v>0.33935</v>
+      </c>
+      <c r="CF135" t="n">
+        <v>0.35823</v>
+      </c>
+      <c r="CG135" t="n">
+        <v>0.33335</v>
+      </c>
+      <c r="CH135" t="n">
+        <v>0.51386</v>
+      </c>
+      <c r="CI135" t="n">
+        <v>0.38949</v>
+      </c>
+      <c r="CJ135" t="n">
+        <v>0.43879</v>
+      </c>
+      <c r="CK135" t="n">
+        <v>0.34939</v>
+      </c>
+      <c r="CL135" t="n">
+        <v>0.33764</v>
+      </c>
+      <c r="CM135" t="n">
+        <v>0.32397</v>
+      </c>
+      <c r="CN135" t="n">
+        <v>0.33497</v>
+      </c>
+      <c r="CO135" t="n">
+        <v>0.32656</v>
+      </c>
+      <c r="CP135" t="n">
+        <v>0.30559</v>
+      </c>
+      <c r="CQ135" t="n">
+        <v>0.33117</v>
+      </c>
+      <c r="CR135" t="n">
+        <v>0.30539</v>
+      </c>
+      <c r="CS135" t="n">
+        <v>0.32155</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="B136" t="n">
+        <v>0.30027</v>
+      </c>
+      <c r="C136" t="n">
+        <v>0.77858</v>
+      </c>
+      <c r="D136" t="n">
+        <v>0.32702</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0.32684</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0.32961</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0.33155</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0.26723</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0.29172</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0.2873</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0.3058999999999999</v>
+      </c>
+      <c r="L136" t="n">
+        <v>0.23558</v>
+      </c>
+      <c r="M136" t="n">
+        <v>0.2851</v>
+      </c>
+      <c r="N136" t="n">
+        <v>0.2929</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0.28886</v>
+      </c>
+      <c r="P136" t="n">
+        <v>0.24609</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>0.23468</v>
+      </c>
+      <c r="R136" t="n">
+        <v>0.2377</v>
+      </c>
+      <c r="S136" t="n">
+        <v>0.23769</v>
+      </c>
+      <c r="T136" t="n">
+        <v>0.2345</v>
+      </c>
+      <c r="U136" t="n">
+        <v>0.2345</v>
+      </c>
+      <c r="V136" t="n">
+        <v>0.23641</v>
+      </c>
+      <c r="W136" t="n">
+        <v>0.28064</v>
+      </c>
+      <c r="X136" t="n">
+        <v>0.23088</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>0.2345</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>0.23481</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>0.27982</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>0.23482</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>0.23462</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>0.32606</v>
+      </c>
+      <c r="AE136" t="n">
+        <v>0.24158</v>
+      </c>
+      <c r="AF136" t="n">
+        <v>0.16087</v>
+      </c>
+      <c r="AG136" t="n">
+        <v>0.26616</v>
+      </c>
+      <c r="AH136" t="n">
+        <v>0.20786</v>
+      </c>
+      <c r="AI136" t="n">
+        <v>0.01227</v>
+      </c>
+      <c r="AJ136" t="n">
+        <v>0.00044</v>
+      </c>
+      <c r="AK136" t="n">
+        <v>-0.00031</v>
+      </c>
+      <c r="AL136" t="n">
+        <v>-0.04957</v>
+      </c>
+      <c r="AM136" t="n">
+        <v>0.14553</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>0.02116</v>
+      </c>
+      <c r="AO136" t="n">
+        <v>-0.03957</v>
+      </c>
+      <c r="AP136" t="n">
+        <v>-0.04959</v>
+      </c>
+      <c r="AQ136" t="n">
+        <v>-0.01539</v>
+      </c>
+      <c r="AR136" t="n">
+        <v>-0.04284</v>
+      </c>
+      <c r="AS136" t="n">
+        <v>-0.04073</v>
+      </c>
+      <c r="AT136" t="n">
+        <v>-0.04858</v>
+      </c>
+      <c r="AU136" t="n">
+        <v>-0.04823</v>
+      </c>
+      <c r="AV136" t="n">
+        <v>-0.02446</v>
+      </c>
+      <c r="AW136" t="n">
+        <v>-0.02922</v>
+      </c>
+      <c r="AX136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY136" t="n">
+        <v>-0.04961</v>
+      </c>
+      <c r="AZ136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA136" t="n">
+        <v>-0.04959</v>
+      </c>
+      <c r="BB136" t="n">
+        <v>-0.0496</v>
+      </c>
+      <c r="BC136" t="n">
+        <v>-0.0494</v>
+      </c>
+      <c r="BD136" t="n">
+        <v>0.00013</v>
+      </c>
+      <c r="BE136" t="n">
+        <v>0.27415</v>
+      </c>
+      <c r="BF136" t="n">
+        <v>-0.04964</v>
+      </c>
+      <c r="BG136" t="n">
+        <v>-0.0493</v>
+      </c>
+      <c r="BH136" t="n">
+        <v>-0.0496</v>
+      </c>
+      <c r="BI136" t="n">
+        <v>-0.03836999999999999</v>
+      </c>
+      <c r="BJ136" t="n">
+        <v>-0.01911</v>
+      </c>
+      <c r="BK136" t="n">
+        <v>-0.04958</v>
+      </c>
+      <c r="BL136" t="n">
+        <v>-0.04963</v>
+      </c>
+      <c r="BM136" t="n">
+        <v>-0.03618</v>
+      </c>
+      <c r="BN136" t="n">
+        <v>0.20124</v>
+      </c>
+      <c r="BO136" t="n">
+        <v>0.26459</v>
+      </c>
+      <c r="BP136" t="n">
+        <v>0.28813</v>
+      </c>
+      <c r="BQ136" t="n">
+        <v>0.27912</v>
+      </c>
+      <c r="BR136" t="n">
+        <v>0.30375</v>
+      </c>
+      <c r="BS136" t="n">
+        <v>0.3077</v>
+      </c>
+      <c r="BT136" t="n">
+        <v>0.23884</v>
+      </c>
+      <c r="BU136" t="n">
+        <v>0.3102200000000001</v>
+      </c>
+      <c r="BV136" t="n">
+        <v>0.32789</v>
+      </c>
+      <c r="BW136" t="n">
+        <v>0.34323</v>
+      </c>
+      <c r="BX136" t="n">
+        <v>0.33616</v>
+      </c>
+      <c r="BY136" t="n">
+        <v>0.33956</v>
+      </c>
+      <c r="BZ136" t="n">
+        <v>0.30939</v>
+      </c>
+      <c r="CA136" t="n">
+        <v>0.31453</v>
+      </c>
+      <c r="CB136" t="n">
+        <v>0.34899</v>
+      </c>
+      <c r="CC136" t="n">
+        <v>0.33773</v>
+      </c>
+      <c r="CD136" t="n">
+        <v>0.34192</v>
+      </c>
+      <c r="CE136" t="n">
+        <v>0.33964</v>
+      </c>
+      <c r="CF136" t="n">
+        <v>0.33794</v>
+      </c>
+      <c r="CG136" t="n">
+        <v>0.34333</v>
+      </c>
+      <c r="CH136" t="n">
+        <v>0.33748</v>
+      </c>
+      <c r="CI136" t="n">
+        <v>0.36399</v>
+      </c>
+      <c r="CJ136" t="n">
+        <v>0.41717</v>
+      </c>
+      <c r="CK136" t="n">
+        <v>0.35222</v>
+      </c>
+      <c r="CL136" t="n">
+        <v>0.36609</v>
+      </c>
+      <c r="CM136" t="n">
+        <v>0.34763</v>
+      </c>
+      <c r="CN136" t="n">
+        <v>0.34306</v>
+      </c>
+      <c r="CO136" t="n">
+        <v>0.34251</v>
+      </c>
+      <c r="CP136" t="n">
+        <v>0.33459</v>
+      </c>
+      <c r="CQ136" t="n">
+        <v>0.34459</v>
+      </c>
+      <c r="CR136" t="n">
+        <v>0.31176</v>
+      </c>
+      <c r="CS136" t="n">
+        <v>0.32927</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B137" t="n">
+        <v>0.29801</v>
+      </c>
+      <c r="C137" t="n">
+        <v>0.72278</v>
+      </c>
+      <c r="D137" t="n">
+        <v>0.62098</v>
+      </c>
+      <c r="E137" t="n">
+        <v>0.38353</v>
+      </c>
+      <c r="F137" t="n">
+        <v>0.41661</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0.39022</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0.41148</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0.41892</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0.35836</v>
+      </c>
+      <c r="K137" t="n">
+        <v>0.29393</v>
+      </c>
+      <c r="L137" t="n">
+        <v>0.33813</v>
+      </c>
+      <c r="M137" t="n">
+        <v>0.30586</v>
+      </c>
+      <c r="N137" t="n">
+        <v>0.3042</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0.29961</v>
+      </c>
+      <c r="P137" t="n">
+        <v>0.25722</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>0.29995</v>
+      </c>
+      <c r="R137" t="n">
+        <v>0.28369</v>
+      </c>
+      <c r="S137" t="n">
+        <v>0.25668</v>
+      </c>
+      <c r="T137" t="n">
+        <v>0.23449</v>
+      </c>
+      <c r="U137" t="n">
+        <v>0.26898</v>
+      </c>
+      <c r="V137" t="n">
+        <v>0.25922</v>
+      </c>
+      <c r="W137" t="n">
+        <v>0.28812</v>
+      </c>
+      <c r="X137" t="n">
+        <v>0.25449</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>0.27985</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>0.29154</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>0.3142200000000001</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>0.43583</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>0.35451</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>0.33956</v>
+      </c>
+      <c r="AE137" t="n">
+        <v>0.34546</v>
+      </c>
+      <c r="AF137" t="n">
+        <v>0.25929</v>
+      </c>
+      <c r="AG137" t="n">
+        <v>0.36395</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>0.6567799999999999</v>
+      </c>
+      <c r="AI137" t="n">
+        <v>0.82278</v>
+      </c>
+      <c r="AJ137" t="n">
+        <v>0.8757200000000001</v>
+      </c>
+      <c r="AK137" t="n">
+        <v>0.84934</v>
+      </c>
+      <c r="AL137" t="n">
+        <v>0.32529</v>
+      </c>
+      <c r="AM137" t="n">
+        <v>0.38107</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>0.1227</v>
+      </c>
+      <c r="AO137" t="n">
+        <v>0.21449</v>
+      </c>
+      <c r="AP137" t="n">
+        <v>0.2981</v>
+      </c>
+      <c r="AQ137" t="n">
+        <v>0.31208</v>
+      </c>
+      <c r="AR137" t="n">
+        <v>0.29656</v>
+      </c>
+      <c r="AS137" t="n">
+        <v>0.2987</v>
+      </c>
+      <c r="AT137" t="n">
+        <v>0.26619</v>
+      </c>
+      <c r="AU137" t="n">
+        <v>0.3002</v>
+      </c>
+      <c r="AV137" t="n">
+        <v>0.34454</v>
+      </c>
+      <c r="AW137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY137" t="n">
+        <v>0.25771</v>
+      </c>
+      <c r="AZ137" t="n">
+        <v>0.27138</v>
+      </c>
+      <c r="BA137" t="n">
+        <v>0.01463</v>
+      </c>
+      <c r="BB137" t="n">
+        <v>0.27357</v>
+      </c>
+      <c r="BC137" t="n">
+        <v>0.00534</v>
+      </c>
+      <c r="BD137" t="n">
+        <v>0.31171</v>
+      </c>
+      <c r="BE137" t="n">
+        <v>0.31546</v>
+      </c>
+      <c r="BF137" t="n">
+        <v>0.2912</v>
+      </c>
+      <c r="BG137" t="n">
+        <v>0.06347</v>
+      </c>
+      <c r="BH137" t="n">
+        <v>0.28588</v>
+      </c>
+      <c r="BI137" t="n">
+        <v>0.30007</v>
+      </c>
+      <c r="BJ137" t="n">
+        <v>0.28885</v>
+      </c>
+      <c r="BK137" t="n">
+        <v>0.30316</v>
+      </c>
+      <c r="BL137" t="n">
+        <v>0.25718</v>
+      </c>
+      <c r="BM137" t="n">
+        <v>0.29371</v>
+      </c>
+      <c r="BN137" t="n">
+        <v>0.47104</v>
+      </c>
+      <c r="BO137" t="n">
+        <v>0.33051</v>
+      </c>
+      <c r="BP137" t="n">
+        <v>0.32465</v>
+      </c>
+      <c r="BQ137" t="n">
+        <v>0.35462</v>
+      </c>
+      <c r="BR137" t="n">
+        <v>0.38418</v>
+      </c>
+      <c r="BS137" t="n">
+        <v>0.39597</v>
+      </c>
+      <c r="BT137" t="n">
+        <v>0.35337</v>
+      </c>
+      <c r="BU137" t="n">
+        <v>0.37756</v>
+      </c>
+      <c r="BV137" t="n">
+        <v>0.36776</v>
+      </c>
+      <c r="BW137" t="n">
+        <v>0.39759</v>
+      </c>
+      <c r="BX137" t="n">
+        <v>1.49006</v>
+      </c>
+      <c r="BY137" t="n">
+        <v>0.79165</v>
+      </c>
+      <c r="BZ137" t="n">
+        <v>0.75185</v>
+      </c>
+      <c r="CA137" t="n">
+        <v>0.7747200000000001</v>
+      </c>
+      <c r="CB137" t="n">
+        <v>1.34046</v>
+      </c>
+      <c r="CC137" t="n">
+        <v>0.99483</v>
+      </c>
+      <c r="CD137" t="n">
+        <v>0.75817</v>
+      </c>
+      <c r="CE137" t="n">
+        <v>0.83604</v>
+      </c>
+      <c r="CF137" t="n">
+        <v>0.78304</v>
+      </c>
+      <c r="CG137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH137" t="n">
+        <v>0.83975</v>
+      </c>
+      <c r="CI137" t="n">
+        <v>0.83794</v>
+      </c>
+      <c r="CJ137" t="n">
+        <v>0.8422500000000001</v>
+      </c>
+      <c r="CK137" t="n">
+        <v>0.93948</v>
+      </c>
+      <c r="CL137" t="n">
+        <v>0.7422000000000001</v>
+      </c>
+      <c r="CM137" t="n">
+        <v>0.77899</v>
+      </c>
+      <c r="CN137" t="n">
+        <v>0.7454700000000001</v>
+      </c>
+      <c r="CO137" t="n">
+        <v>0.38106</v>
+      </c>
+      <c r="CP137" t="n">
+        <v>0.3547</v>
+      </c>
+      <c r="CQ137" t="n">
+        <v>0.37164</v>
+      </c>
+      <c r="CR137" t="n">
+        <v>0.36235</v>
+      </c>
+      <c r="CS137" t="n">
+        <v>0.36218</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B138" t="n">
+        <v>0.33007</v>
+      </c>
+      <c r="C138" t="n">
+        <v>0.46287</v>
+      </c>
+      <c r="D138" t="n">
+        <v>0.60277</v>
+      </c>
+      <c r="E138" t="n">
+        <v>0.6345499999999999</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0.56497</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0.49295</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0.45748</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0.39947</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0.38909</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0.38023</v>
+      </c>
+      <c r="L138" t="n">
+        <v>0.37013</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0.35258</v>
+      </c>
+      <c r="N138" t="n">
+        <v>0.33094</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0.33518</v>
+      </c>
+      <c r="P138" t="n">
+        <v>0.32459</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>0.31696</v>
+      </c>
+      <c r="R138" t="n">
+        <v>0.47165</v>
+      </c>
+      <c r="S138" t="n">
+        <v>0.31866</v>
+      </c>
+      <c r="T138" t="n">
+        <v>0.3127200000000001</v>
+      </c>
+      <c r="U138" t="n">
+        <v>0.31271</v>
+      </c>
+      <c r="V138" t="n">
+        <v>0.30357</v>
+      </c>
+      <c r="W138" t="n">
+        <v>0.30803</v>
+      </c>
+      <c r="X138" t="n">
+        <v>0.27505</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>0.33939</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>0.33717</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>0.36305</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>0.45815</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>0.46844</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>0.364</v>
+      </c>
+      <c r="AE138" t="n">
+        <v>0.381</v>
+      </c>
+      <c r="AF138" t="n">
+        <v>0.32139</v>
+      </c>
+      <c r="AG138" t="n">
+        <v>0.32184</v>
+      </c>
+      <c r="AH138" t="n">
+        <v>0.33081</v>
+      </c>
+      <c r="AI138" t="n">
+        <v>0.42086</v>
+      </c>
+      <c r="AJ138" t="n">
+        <v>0.37467</v>
+      </c>
+      <c r="AK138" t="n">
+        <v>0.44751</v>
+      </c>
+      <c r="AL138" t="n">
+        <v>0.37725</v>
+      </c>
+      <c r="AM138" t="n">
+        <v>0.41985</v>
+      </c>
+      <c r="AN138" t="n">
+        <v>0.3983</v>
+      </c>
+      <c r="AO138" t="n">
+        <v>0.37838</v>
+      </c>
+      <c r="AP138" t="n">
+        <v>0.35866</v>
+      </c>
+      <c r="AQ138" t="n">
+        <v>0.34554</v>
+      </c>
+      <c r="AR138" t="n">
+        <v>0.39757</v>
+      </c>
+      <c r="AS138" t="n">
+        <v>0.35293</v>
+      </c>
+      <c r="AT138" t="n">
+        <v>0.32471</v>
+      </c>
+      <c r="AU138" t="n">
+        <v>0.32532</v>
+      </c>
+      <c r="AV138" t="n">
+        <v>0.34218</v>
+      </c>
+      <c r="AW138" t="n">
+        <v>0.32239</v>
+      </c>
+      <c r="AX138" t="n">
+        <v>0.27508</v>
+      </c>
+      <c r="AY138" t="n">
+        <v>0.32508</v>
+      </c>
+      <c r="AZ138" t="n">
+        <v>0.31619</v>
+      </c>
+      <c r="BA138" t="n">
+        <v>0.31764</v>
+      </c>
+      <c r="BB138" t="n">
+        <v>0.32749</v>
+      </c>
+      <c r="BC138" t="n">
+        <v>0.33705</v>
+      </c>
+      <c r="BD138" t="n">
+        <v>0.33464</v>
+      </c>
+      <c r="BE138" t="n">
+        <v>0.36493</v>
+      </c>
+      <c r="BF138" t="n">
+        <v>0.33123</v>
+      </c>
+      <c r="BG138" t="n">
+        <v>0.32839</v>
+      </c>
+      <c r="BH138" t="n">
+        <v>0.31592</v>
+      </c>
+      <c r="BI138" t="n">
+        <v>0.31708</v>
+      </c>
+      <c r="BJ138" t="n">
+        <v>0.32242</v>
+      </c>
+      <c r="BK138" t="n">
+        <v>0.33467</v>
+      </c>
+      <c r="BL138" t="n">
+        <v>0.33819</v>
+      </c>
+      <c r="BM138" t="n">
+        <v>0.33573</v>
+      </c>
+      <c r="BN138" t="n">
+        <v>0.34153</v>
+      </c>
+      <c r="BO138" t="n">
+        <v>0.3369</v>
+      </c>
+      <c r="BP138" t="n">
+        <v>0.35253</v>
+      </c>
+      <c r="BQ138" t="n">
+        <v>0.36593</v>
+      </c>
+      <c r="BR138" t="n">
+        <v>0.37114</v>
+      </c>
+      <c r="BS138" t="n">
+        <v>0.38133</v>
+      </c>
+      <c r="BT138" t="n">
+        <v>0.37176</v>
+      </c>
+      <c r="BU138" t="n">
+        <v>0.37196</v>
+      </c>
+      <c r="BV138" t="n">
+        <v>0.34098</v>
+      </c>
+      <c r="BW138" t="n">
+        <v>0.36729</v>
+      </c>
+      <c r="BX138" t="n">
+        <v>0.40706</v>
+      </c>
+      <c r="BY138" t="n">
+        <v>0.39456</v>
+      </c>
+      <c r="BZ138" t="n">
+        <v>0.38017</v>
+      </c>
+      <c r="CA138" t="n">
+        <v>0.35425</v>
+      </c>
+      <c r="CB138" t="n">
+        <v>0.37989</v>
+      </c>
+      <c r="CC138" t="n">
+        <v>0.39669</v>
+      </c>
+      <c r="CD138" t="n">
+        <v>0.45437</v>
+      </c>
+      <c r="CE138" t="n">
+        <v>0.46293</v>
+      </c>
+      <c r="CF138" t="n">
+        <v>0.72972</v>
+      </c>
+      <c r="CG138" t="n">
+        <v>0.42852</v>
+      </c>
+      <c r="CH138" t="n">
+        <v>0.60193</v>
+      </c>
+      <c r="CI138" t="n">
+        <v>0.46876</v>
+      </c>
+      <c r="CJ138" t="n">
+        <v>0.4030899999999999</v>
+      </c>
+      <c r="CK138" t="n">
+        <v>0.42326</v>
+      </c>
+      <c r="CL138" t="n">
+        <v>0.4074</v>
+      </c>
+      <c r="CM138" t="n">
+        <v>0.38756</v>
+      </c>
+      <c r="CN138" t="n">
+        <v>0.46748</v>
+      </c>
+      <c r="CO138" t="n">
+        <v>0.35198</v>
+      </c>
+      <c r="CP138" t="n">
+        <v>0.35552</v>
+      </c>
+      <c r="CQ138" t="n">
+        <v>0.33845</v>
+      </c>
+      <c r="CR138" t="n">
+        <v>0.33999</v>
+      </c>
+      <c r="CS138" t="n">
+        <v>0.33663</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B139" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="C139" t="n">
+        <v>0.41873</v>
+      </c>
+      <c r="D139" t="n">
+        <v>0.42167</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0.40643</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0.38945</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0.38228</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0.37822</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0.37556</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0.35619</v>
+      </c>
+      <c r="K139" t="n">
+        <v>0.35873</v>
+      </c>
+      <c r="L139" t="n">
+        <v>0.35131</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0.35097</v>
+      </c>
+      <c r="N139" t="n">
+        <v>0.34543</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0.3475</v>
+      </c>
+      <c r="P139" t="n">
+        <v>0.34531</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>0.34098</v>
+      </c>
+      <c r="R139" t="n">
+        <v>0.35149</v>
+      </c>
+      <c r="S139" t="n">
+        <v>0.3356</v>
+      </c>
+      <c r="T139" t="n">
+        <v>0.33485</v>
+      </c>
+      <c r="U139" t="n">
+        <v>0.3289</v>
+      </c>
+      <c r="V139" t="n">
+        <v>0.33077</v>
+      </c>
+      <c r="W139" t="n">
+        <v>0.33226</v>
+      </c>
+      <c r="X139" t="n">
+        <v>0.33234</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>0.34243</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>0.33477</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>0.3504</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>0.34336</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>0.35111</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>0.34431</v>
+      </c>
+      <c r="AE139" t="n">
+        <v>0.35386</v>
+      </c>
+      <c r="AF139" t="n">
+        <v>0.40342</v>
+      </c>
+      <c r="AG139" t="n">
+        <v>0.36482</v>
+      </c>
+      <c r="AH139" t="n">
+        <v>0.35537</v>
+      </c>
+      <c r="AI139" t="n">
+        <v>0.54655</v>
+      </c>
+      <c r="AJ139" t="n">
+        <v>0.7581</v>
+      </c>
+      <c r="AK139" t="n">
+        <v>0.5394500000000001</v>
+      </c>
+      <c r="AL139" t="n">
+        <v>0.5289400000000001</v>
+      </c>
+      <c r="AM139" t="n">
+        <v>0.56143</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>0.4495</v>
+      </c>
+      <c r="AO139" t="n">
+        <v>0.38585</v>
+      </c>
+      <c r="AP139" t="n">
+        <v>0.37427</v>
+      </c>
+      <c r="AQ139" t="n">
+        <v>0.36374</v>
+      </c>
+      <c r="AR139" t="n">
+        <v>0.3542</v>
+      </c>
+      <c r="AS139" t="n">
+        <v>0.36245</v>
+      </c>
+      <c r="AT139" t="n">
+        <v>0.42518</v>
+      </c>
+      <c r="AU139" t="n">
+        <v>0.36018</v>
+      </c>
+      <c r="AV139" t="n">
+        <v>0.39325</v>
+      </c>
+      <c r="AW139" t="n">
+        <v>0.35686</v>
+      </c>
+      <c r="AX139" t="n">
+        <v>0.31126</v>
+      </c>
+      <c r="AY139" t="n">
+        <v>0.49816</v>
+      </c>
+      <c r="AZ139" t="n">
+        <v>0.47148</v>
+      </c>
+      <c r="BA139" t="n">
+        <v>0.49067</v>
+      </c>
+      <c r="BB139" t="n">
+        <v>0.50569</v>
+      </c>
+      <c r="BC139" t="n">
+        <v>0.4244</v>
+      </c>
+      <c r="BD139" t="n">
+        <v>0.34881</v>
+      </c>
+      <c r="BE139" t="n">
+        <v>0.47924</v>
+      </c>
+      <c r="BF139" t="n">
+        <v>0.33383</v>
+      </c>
+      <c r="BG139" t="n">
+        <v>0.33151</v>
+      </c>
+      <c r="BH139" t="n">
+        <v>0.47446</v>
+      </c>
+      <c r="BI139" t="n">
+        <v>0.35192</v>
+      </c>
+      <c r="BJ139" t="n">
+        <v>0.33699</v>
+      </c>
+      <c r="BK139" t="n">
+        <v>0.34149</v>
+      </c>
+      <c r="BL139" t="n">
+        <v>0.33084</v>
+      </c>
+      <c r="BM139" t="n">
+        <v>0.35264</v>
+      </c>
+      <c r="BN139" t="n">
+        <v>0.3524</v>
+      </c>
+      <c r="BO139" t="n">
+        <v>1.20407</v>
+      </c>
+      <c r="BP139" t="n">
+        <v>0.69676</v>
+      </c>
+      <c r="BQ139" t="n">
+        <v>0.49105</v>
+      </c>
+      <c r="BR139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BS139" t="n">
+        <v>1.11266</v>
+      </c>
+      <c r="BT139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BU139" t="n">
+        <v>0.9768</v>
+      </c>
+      <c r="BV139" t="n">
+        <v>1.35736</v>
+      </c>
+      <c r="BW139" t="n">
+        <v>0.8424299999999999</v>
+      </c>
+      <c r="BX139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BY139" t="n">
+        <v>1.2152</v>
+      </c>
+      <c r="BZ139" t="n">
+        <v>1.17923</v>
+      </c>
+      <c r="CA139" t="n">
+        <v>0.7203200000000001</v>
+      </c>
+      <c r="CB139" t="n">
+        <v>0.56548</v>
+      </c>
+      <c r="CC139" t="n">
+        <v>0.45385</v>
+      </c>
+      <c r="CD139" t="n">
+        <v>0.45208</v>
+      </c>
+      <c r="CE139" t="n">
+        <v>0.70858</v>
+      </c>
+      <c r="CF139" t="n">
+        <v>0.8680399999999999</v>
+      </c>
+      <c r="CG139" t="n">
+        <v>1.03446</v>
+      </c>
+      <c r="CH139" t="n">
+        <v>0.51958</v>
+      </c>
+      <c r="CI139" t="n">
+        <v>0.45564</v>
+      </c>
+      <c r="CJ139" t="n">
+        <v>0.3521</v>
+      </c>
+      <c r="CK139" t="n">
+        <v>0.41833</v>
+      </c>
+      <c r="CL139" t="n">
+        <v>0.37748</v>
+      </c>
+      <c r="CM139" t="n">
+        <v>0.35548</v>
+      </c>
+      <c r="CN139" t="n">
+        <v>0.37929</v>
+      </c>
+      <c r="CO139" t="n">
+        <v>0.3627</v>
+      </c>
+      <c r="CP139" t="n">
+        <v>0.23413</v>
+      </c>
+      <c r="CQ139" t="n">
+        <v>0.35513</v>
+      </c>
+      <c r="CR139" t="n">
+        <v>0.3432</v>
+      </c>
+      <c r="CS139" t="n">
+        <v>0.35144</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B140" t="n">
+        <v>0.3374</v>
+      </c>
+      <c r="C140" t="n">
+        <v>0.4525</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0.38049</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0.37643</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0.36886</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0.36429</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0.34587</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0.35559</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0.36488</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0.35998</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0.35841</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0.35743</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0.35049</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0.34697</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0.3447</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>0.34602</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0.34564</v>
+      </c>
+      <c r="S140" t="n">
+        <v>0.33889</v>
+      </c>
+      <c r="T140" t="n">
+        <v>0.31879</v>
+      </c>
+      <c r="U140" t="n">
+        <v>0.3391</v>
+      </c>
+      <c r="V140" t="n">
+        <v>0.33354</v>
+      </c>
+      <c r="W140" t="n">
+        <v>0.33147</v>
+      </c>
+      <c r="X140" t="n">
+        <v>0.32965</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>0.3400899999999999</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>0.33851</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>0.34854</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>0.36965</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>0.35129</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>0.35586</v>
+      </c>
+      <c r="AE140" t="n">
+        <v>0.344</v>
+      </c>
+      <c r="AF140" t="n">
+        <v>0.35047</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>0.34901</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>0.34792</v>
+      </c>
+      <c r="AI140" t="n">
+        <v>0.38029</v>
+      </c>
+      <c r="AJ140" t="n">
+        <v>0.3913</v>
+      </c>
+      <c r="AK140" t="n">
+        <v>0.36483</v>
+      </c>
+      <c r="AL140" t="n">
+        <v>0.35395</v>
+      </c>
+      <c r="AM140" t="n">
+        <v>0.43504</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>0.38001</v>
+      </c>
+      <c r="AO140" t="n">
+        <v>0.36182</v>
+      </c>
+      <c r="AP140" t="n">
+        <v>0.37446</v>
+      </c>
+      <c r="AQ140" t="n">
+        <v>0.35476</v>
+      </c>
+      <c r="AR140" t="n">
+        <v>0.31056</v>
+      </c>
+      <c r="AS140" t="n">
+        <v>0.36362</v>
+      </c>
+      <c r="AT140" t="n">
+        <v>1.17157</v>
+      </c>
+      <c r="AU140" t="n">
+        <v>0.41658</v>
+      </c>
+      <c r="AV140" t="n">
+        <v>0.64127</v>
+      </c>
+      <c r="AW140" t="n">
+        <v>0.43481</v>
+      </c>
+      <c r="AX140" t="n">
+        <v>0.29259</v>
+      </c>
+      <c r="AY140" t="n">
+        <v>0.6881</v>
+      </c>
+      <c r="AZ140" t="n">
+        <v>0.48473</v>
+      </c>
+      <c r="BA140" t="n">
+        <v>0.40683</v>
+      </c>
+      <c r="BB140" t="n">
+        <v>0.56057</v>
+      </c>
+      <c r="BC140" t="n">
+        <v>0.31619</v>
+      </c>
+      <c r="BD140" t="n">
+        <v>0.33659</v>
+      </c>
+      <c r="BE140" t="n">
+        <v>0.34369</v>
+      </c>
+      <c r="BF140" t="n">
+        <v>0.32531</v>
+      </c>
+      <c r="BG140" t="n">
+        <v>0.33354</v>
+      </c>
+      <c r="BH140" t="n">
+        <v>0.34178</v>
+      </c>
+      <c r="BI140" t="n">
+        <v>0.33826</v>
+      </c>
+      <c r="BJ140" t="n">
+        <v>0.32488</v>
+      </c>
+      <c r="BK140" t="n">
+        <v>0.34423</v>
+      </c>
+      <c r="BL140" t="n">
+        <v>0.34325</v>
+      </c>
+      <c r="BM140" t="n">
+        <v>0.36816</v>
+      </c>
+      <c r="BN140" t="n">
+        <v>0.36496</v>
+      </c>
+      <c r="BO140" t="n">
+        <v>0.3713399999999999</v>
+      </c>
+      <c r="BP140" t="n">
+        <v>0.48583</v>
+      </c>
+      <c r="BQ140" t="n">
+        <v>0.37527</v>
+      </c>
+      <c r="BR140" t="n">
+        <v>0.39425</v>
+      </c>
+      <c r="BS140" t="n">
+        <v>0.37325</v>
+      </c>
+      <c r="BT140" t="n">
+        <v>0.37418</v>
+      </c>
+      <c r="BU140" t="n">
+        <v>0.41772</v>
+      </c>
+      <c r="BV140" t="n">
+        <v>0.41201</v>
+      </c>
+      <c r="BW140" t="n">
+        <v>0.5136499999999999</v>
+      </c>
+      <c r="BX140" t="n">
+        <v>0.9107999999999999</v>
+      </c>
+      <c r="BY140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BZ140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CA140" t="n">
+        <v>0.70557</v>
+      </c>
+      <c r="CB140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CC140" t="n">
+        <v>0.7759199999999999</v>
+      </c>
+      <c r="CD140" t="n">
+        <v>1.2721</v>
+      </c>
+      <c r="CE140" t="n">
+        <v>0.62766</v>
+      </c>
+      <c r="CF140" t="n">
+        <v>0.47504</v>
+      </c>
+      <c r="CG140" t="n">
+        <v>1.41299</v>
+      </c>
+      <c r="CH140" t="n">
+        <v>1.03407</v>
+      </c>
+      <c r="CI140" t="n">
+        <v>1.2529</v>
+      </c>
+      <c r="CJ140" t="n">
+        <v>1.14564</v>
+      </c>
+      <c r="CK140" t="n">
+        <v>1.06868</v>
+      </c>
+      <c r="CL140" t="n">
+        <v>0.80198</v>
+      </c>
+      <c r="CM140" t="n">
+        <v>0.77595</v>
+      </c>
+      <c r="CN140" t="n">
+        <v>0.7489199999999999</v>
+      </c>
+      <c r="CO140" t="n">
+        <v>0.44121</v>
+      </c>
+      <c r="CP140" t="n">
+        <v>0.35852</v>
+      </c>
+      <c r="CQ140" t="n">
+        <v>0.36221</v>
+      </c>
+      <c r="CR140" t="n">
+        <v>0.3517</v>
+      </c>
+      <c r="CS140" t="n">
+        <v>0.35585</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B141" t="n">
+        <v>0.3007</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0.35692</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0.35872</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0.34761</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0.34891</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0.33944</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0.32623</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0.33748</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0.33105</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0.33212</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0.34255</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0.32239</v>
+      </c>
+      <c r="N141" t="n">
+        <v>0.36568</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0.34232</v>
+      </c>
+      <c r="P141" t="n">
+        <v>0.3319</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>0.33896</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0.33585</v>
+      </c>
+      <c r="S141" t="n">
+        <v>0.22408</v>
+      </c>
+      <c r="T141" t="n">
+        <v>0.32452</v>
+      </c>
+      <c r="U141" t="n">
+        <v>0.32699</v>
+      </c>
+      <c r="V141" t="n">
+        <v>0.33756</v>
+      </c>
+      <c r="W141" t="n">
+        <v>0.32682</v>
+      </c>
+      <c r="X141" t="n">
+        <v>0.33275</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>0.34557</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>0.34321</v>
+      </c>
+      <c r="AA141" t="n">
+        <v>0.33704</v>
+      </c>
+      <c r="AB141" t="n">
+        <v>0.37498</v>
+      </c>
+      <c r="AC141" t="n">
+        <v>0.37484</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>0.35246</v>
+      </c>
+      <c r="AE141" t="n">
+        <v>0.33954</v>
+      </c>
+      <c r="AF141" t="n">
+        <v>0.33709</v>
+      </c>
+      <c r="AG141" t="n">
+        <v>0.33791</v>
+      </c>
+      <c r="AH141" t="n">
+        <v>0.36195</v>
+      </c>
+      <c r="AI141" t="n">
+        <v>0.33473</v>
+      </c>
+      <c r="AJ141" t="n">
+        <v>0.34829</v>
+      </c>
+      <c r="AK141" t="n">
+        <v>0.35145</v>
+      </c>
+      <c r="AL141" t="n">
+        <v>0.33558</v>
+      </c>
+      <c r="AM141" t="n">
+        <v>0.34515</v>
+      </c>
+      <c r="AN141" t="n">
+        <v>0.46869</v>
+      </c>
+      <c r="AO141" t="n">
+        <v>1.77184</v>
+      </c>
+      <c r="AP141" t="n">
+        <v>1.20604</v>
+      </c>
+      <c r="AQ141" t="n">
+        <v>0.5869800000000001</v>
+      </c>
+      <c r="AR141" t="n">
+        <v>1.01178</v>
+      </c>
+      <c r="AS141" t="n">
+        <v>1.21996</v>
+      </c>
+      <c r="AT141" t="n">
+        <v>0.62278</v>
+      </c>
+      <c r="AU141" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AV141" t="n">
+        <v>1.78171</v>
+      </c>
+      <c r="AW141" t="n">
+        <v>1.32558</v>
+      </c>
+      <c r="AX141" t="n">
+        <v>0.45385</v>
+      </c>
+      <c r="AY141" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AZ141" t="n">
+        <v>0.5912500000000001</v>
+      </c>
+      <c r="BA141" t="n">
+        <v>0.56077</v>
+      </c>
+      <c r="BB141" t="n">
+        <v>1.39759</v>
+      </c>
+      <c r="BC141" t="n">
+        <v>0.68114</v>
+      </c>
+      <c r="BD141" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BE141" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BF141" t="n">
+        <v>1.22328</v>
+      </c>
+      <c r="BG141" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BH141" t="n">
+        <v>0.58708</v>
+      </c>
+      <c r="BI141" t="n">
+        <v>1.21033</v>
+      </c>
+      <c r="BJ141" t="n">
+        <v>1.44069</v>
+      </c>
+      <c r="BK141" t="n">
+        <v>1.22705</v>
+      </c>
+      <c r="BL141" t="n">
+        <v>0.6076699999999999</v>
+      </c>
+      <c r="BM141" t="n">
+        <v>0.34813</v>
+      </c>
+      <c r="BN141" t="n">
+        <v>0.3408</v>
+      </c>
+      <c r="BO141" t="n">
+        <v>0.47412</v>
+      </c>
+      <c r="BP141" t="n">
+        <v>0.43306</v>
+      </c>
+      <c r="BQ141" t="n">
+        <v>0.3614</v>
+      </c>
+      <c r="BR141" t="n">
+        <v>0.48207</v>
+      </c>
+      <c r="BS141" t="n">
+        <v>1.18119</v>
+      </c>
+      <c r="BT141" t="n">
+        <v>1.00898</v>
+      </c>
+      <c r="BU141" t="n">
+        <v>0.45091</v>
+      </c>
+      <c r="BV141" t="n">
+        <v>0.36574</v>
+      </c>
+      <c r="BW141" t="n">
+        <v>0.37105</v>
+      </c>
+      <c r="BX141" t="n">
+        <v>0.65361</v>
+      </c>
+      <c r="BY141" t="n">
+        <v>1.31363</v>
+      </c>
+      <c r="BZ141" t="n">
+        <v>0.5686100000000001</v>
+      </c>
+      <c r="CA141" t="n">
+        <v>0.67149</v>
+      </c>
+      <c r="CB141" t="n">
+        <v>1.74859</v>
+      </c>
+      <c r="CC141" t="n">
+        <v>0.6982699999999999</v>
+      </c>
+      <c r="CD141" t="n">
+        <v>1.18034</v>
+      </c>
+      <c r="CE141" t="n">
+        <v>0.46588</v>
+      </c>
+      <c r="CF141" t="n">
+        <v>0.7310399999999999</v>
+      </c>
+      <c r="CG141" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH141" t="n">
+        <v>0.67953</v>
+      </c>
+      <c r="CI141" t="n">
+        <v>0.7188</v>
+      </c>
+      <c r="CJ141" t="n">
+        <v>0.68276</v>
+      </c>
+      <c r="CK141" t="n">
+        <v>1.09363</v>
+      </c>
+      <c r="CL141" t="n">
+        <v>0.39824</v>
+      </c>
+      <c r="CM141" t="n">
+        <v>0.45589</v>
+      </c>
+      <c r="CN141" t="n">
+        <v>0.40489</v>
+      </c>
+      <c r="CO141" t="n">
+        <v>0.3689</v>
+      </c>
+      <c r="CP141" t="n">
+        <v>0.398</v>
+      </c>
+      <c r="CQ141" t="n">
+        <v>0.53714</v>
+      </c>
+      <c r="CR141" t="n">
+        <v>0.35265</v>
+      </c>
+      <c r="CS141" t="n">
+        <v>0.36238</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B142" t="n">
+        <v>0.34264</v>
+      </c>
+      <c r="C142" t="n">
+        <v>1.24253</v>
+      </c>
+      <c r="D142" t="n">
+        <v>0.96017</v>
+      </c>
+      <c r="E142" t="n">
+        <v>0.56231</v>
+      </c>
+      <c r="F142" t="n">
+        <v>0.6229</v>
+      </c>
+      <c r="G142" t="n">
+        <v>0.95699</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0.36534</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0.44165</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0.37128</v>
+      </c>
+      <c r="K142" t="n">
+        <v>0.3822</v>
+      </c>
+      <c r="L142" t="n">
+        <v>0.3698</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0.36788</v>
+      </c>
+      <c r="N142" t="n">
+        <v>0.37107</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0.3674</v>
+      </c>
+      <c r="P142" t="n">
+        <v>0.36352</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>0.36771</v>
+      </c>
+      <c r="R142" t="n">
+        <v>0.36725</v>
+      </c>
+      <c r="S142" t="n">
+        <v>0.36617</v>
+      </c>
+      <c r="T142" t="n">
+        <v>0.36682</v>
+      </c>
+      <c r="U142" t="n">
+        <v>0.36239</v>
+      </c>
+      <c r="V142" t="n">
+        <v>0.35689</v>
+      </c>
+      <c r="W142" t="n">
+        <v>0.35881</v>
+      </c>
+      <c r="X142" t="n">
+        <v>0.36133</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>0.35924</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>0.35812</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>0.34876</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>0.35741</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>0.35236</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>0.37046</v>
+      </c>
+      <c r="AE142" t="n">
+        <v>0.35715</v>
+      </c>
+      <c r="AF142" t="n">
+        <v>0.34469</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>0.34692</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>0.35178</v>
+      </c>
+      <c r="AI142" t="n">
+        <v>0.3591</v>
+      </c>
+      <c r="AJ142" t="n">
+        <v>0.36102</v>
+      </c>
+      <c r="AK142" t="n">
+        <v>0.35555</v>
+      </c>
+      <c r="AL142" t="n">
+        <v>0.34201</v>
+      </c>
+      <c r="AM142" t="n">
+        <v>0.37506</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>0.36445</v>
+      </c>
+      <c r="AO142" t="n">
+        <v>0.35718</v>
+      </c>
+      <c r="AP142" t="n">
+        <v>0.36323</v>
+      </c>
+      <c r="AQ142" t="n">
+        <v>0.7955599999999999</v>
+      </c>
+      <c r="AR142" t="n">
+        <v>0.43104</v>
+      </c>
+      <c r="AS142" t="n">
+        <v>0.34981</v>
+      </c>
+      <c r="AT142" t="n">
+        <v>0.35186</v>
+      </c>
+      <c r="AU142" t="n">
+        <v>0.8868200000000001</v>
+      </c>
+      <c r="AV142" t="n">
+        <v>0.325</v>
+      </c>
+      <c r="AW142" t="n">
+        <v>0.34833</v>
+      </c>
+      <c r="AX142" t="n">
+        <v>0.36789</v>
+      </c>
+      <c r="AY142" t="n">
+        <v>0.67431</v>
+      </c>
+      <c r="AZ142" t="n">
+        <v>0.34501</v>
+      </c>
+      <c r="BA142" t="n">
+        <v>0.34158</v>
+      </c>
+      <c r="BB142" t="n">
+        <v>0.47253</v>
+      </c>
+      <c r="BC142" t="n">
+        <v>0.35271</v>
+      </c>
+      <c r="BD142" t="n">
+        <v>0.99762</v>
+      </c>
+      <c r="BE142" t="n">
+        <v>0.72049</v>
+      </c>
+      <c r="BF142" t="n">
+        <v>0.34715</v>
+      </c>
+      <c r="BG142" t="n">
+        <v>0.32255</v>
+      </c>
+      <c r="BH142" t="n">
+        <v>0.33913</v>
+      </c>
+      <c r="BI142" t="n">
+        <v>0.34961</v>
+      </c>
+      <c r="BJ142" t="n">
+        <v>0.32338</v>
+      </c>
+      <c r="BK142" t="n">
+        <v>0.35661</v>
+      </c>
+      <c r="BL142" t="n">
+        <v>0.35858</v>
+      </c>
+      <c r="BM142" t="n">
+        <v>0.3304</v>
+      </c>
+      <c r="BN142" t="n">
+        <v>0.35486</v>
+      </c>
+      <c r="BO142" t="n">
+        <v>0.34586</v>
+      </c>
+      <c r="BP142" t="n">
+        <v>0.35002</v>
+      </c>
+      <c r="BQ142" t="n">
+        <v>0.37539</v>
+      </c>
+      <c r="BR142" t="n">
+        <v>0.46064</v>
+      </c>
+      <c r="BS142" t="n">
+        <v>0.42632</v>
+      </c>
+      <c r="BT142" t="n">
+        <v>0.40368</v>
+      </c>
+      <c r="BU142" t="n">
+        <v>0.38562</v>
+      </c>
+      <c r="BV142" t="n">
+        <v>0.35496</v>
+      </c>
+      <c r="BW142" t="n">
+        <v>0.36272</v>
+      </c>
+      <c r="BX142" t="n">
+        <v>0.38231</v>
+      </c>
+      <c r="BY142" t="n">
+        <v>0.45109</v>
+      </c>
+      <c r="BZ142" t="n">
+        <v>0.48092</v>
+      </c>
+      <c r="CA142" t="n">
+        <v>0.6196799999999999</v>
+      </c>
+      <c r="CB142" t="n">
+        <v>0.5578099999999999</v>
+      </c>
+      <c r="CC142" t="n">
+        <v>0.52685</v>
+      </c>
+      <c r="CD142" t="n">
+        <v>0.45428</v>
+      </c>
+      <c r="CE142" t="n">
+        <v>0.38313</v>
+      </c>
+      <c r="CF142" t="n">
+        <v>0.44681</v>
+      </c>
+      <c r="CG142" t="n">
+        <v>0.47671</v>
+      </c>
+      <c r="CH142" t="n">
+        <v>1.06019</v>
+      </c>
+      <c r="CI142" t="n">
+        <v>1.29963</v>
+      </c>
+      <c r="CJ142" t="n">
+        <v>0.98442</v>
+      </c>
+      <c r="CK142" t="n">
+        <v>0.5401900000000001</v>
+      </c>
+      <c r="CL142" t="n">
+        <v>1.10275</v>
+      </c>
+      <c r="CM142" t="n">
+        <v>1.23533</v>
+      </c>
+      <c r="CN142" t="n">
+        <v>1.16421</v>
+      </c>
+      <c r="CO142" t="n">
+        <v>0.89346</v>
+      </c>
+      <c r="CP142" t="n">
+        <v>0.8962599999999999</v>
+      </c>
+      <c r="CQ142" t="n">
+        <v>0.54941</v>
+      </c>
+      <c r="CR142" t="n">
+        <v>0.54283</v>
+      </c>
+      <c r="CS142" t="n">
+        <v>0.4753500000000001</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B143" t="n">
+        <v>0.34816</v>
+      </c>
+      <c r="C143" t="n">
+        <v>0.8431799999999999</v>
+      </c>
+      <c r="D143" t="n">
+        <v>0.46129</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0.3648</v>
+      </c>
+      <c r="F143" t="n">
+        <v>0.37131</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0.37558</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0.37395</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0.36642</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0.36831</v>
+      </c>
+      <c r="K143" t="n">
+        <v>0.36145</v>
+      </c>
+      <c r="L143" t="n">
+        <v>0.36691</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0.35764</v>
+      </c>
+      <c r="N143" t="n">
+        <v>0.3594</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0.36175</v>
+      </c>
+      <c r="P143" t="n">
+        <v>0.3521</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>0.36488</v>
+      </c>
+      <c r="R143" t="n">
+        <v>0.35148</v>
+      </c>
+      <c r="S143" t="n">
+        <v>0.35687</v>
+      </c>
+      <c r="T143" t="n">
+        <v>0.35579</v>
+      </c>
+      <c r="U143" t="n">
+        <v>0.35665</v>
+      </c>
+      <c r="V143" t="n">
+        <v>0.35256</v>
+      </c>
+      <c r="W143" t="n">
+        <v>0.35287</v>
+      </c>
+      <c r="X143" t="n">
+        <v>0.35505</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>0.35382</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>0.35638</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>0.34774</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>0.34219</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>0.35408</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>0.34833</v>
+      </c>
+      <c r="AE143" t="n">
+        <v>0.34876</v>
+      </c>
+      <c r="AF143" t="n">
+        <v>0.31223</v>
+      </c>
+      <c r="AG143" t="n">
+        <v>0.31703</v>
+      </c>
+      <c r="AH143" t="n">
+        <v>0.31798</v>
+      </c>
+      <c r="AI143" t="n">
+        <v>0.17542</v>
+      </c>
+      <c r="AJ143" t="n">
+        <v>0.30647</v>
+      </c>
+      <c r="AK143" t="n">
+        <v>0.2943</v>
+      </c>
+      <c r="AL143" t="n">
+        <v>0.3103399999999999</v>
+      </c>
+      <c r="AM143" t="n">
+        <v>0.14511</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>0.19771</v>
+      </c>
+      <c r="AO143" t="n">
+        <v>0.14155</v>
+      </c>
+      <c r="AP143" t="n">
+        <v>0.2921</v>
+      </c>
+      <c r="AQ143" t="n">
+        <v>0.04421</v>
+      </c>
+      <c r="AR143" t="n">
+        <v>0.12219</v>
+      </c>
+      <c r="AS143" t="n">
+        <v>0.3309</v>
+      </c>
+      <c r="AT143" t="n">
+        <v>0.22737</v>
+      </c>
+      <c r="AU143" t="n">
+        <v>0.26887</v>
+      </c>
+      <c r="AV143" t="n">
+        <v>0.33158</v>
+      </c>
+      <c r="AW143" t="n">
+        <v>0.5351</v>
+      </c>
+      <c r="AX143" t="n">
+        <v>0.39642</v>
+      </c>
+      <c r="AY143" t="n">
+        <v>0.5289400000000001</v>
+      </c>
+      <c r="AZ143" t="n">
+        <v>0.73753</v>
+      </c>
+      <c r="BA143" t="n">
+        <v>0.52066</v>
+      </c>
+      <c r="BB143" t="n">
+        <v>1.32788</v>
+      </c>
+      <c r="BC143" t="n">
+        <v>0.5837899999999999</v>
+      </c>
+      <c r="BD143" t="n">
+        <v>0.7863600000000001</v>
+      </c>
+      <c r="BE143" t="n">
+        <v>0.7384500000000001</v>
+      </c>
+      <c r="BF143" t="n">
+        <v>0.5827599999999999</v>
+      </c>
+      <c r="BG143" t="n">
+        <v>0.74846</v>
+      </c>
+      <c r="BH143" t="n">
+        <v>0.7289500000000001</v>
+      </c>
+      <c r="BI143" t="n">
+        <v>0.6274500000000001</v>
+      </c>
+      <c r="BJ143" t="n">
+        <v>0.57338</v>
+      </c>
+      <c r="BK143" t="n">
+        <v>0.71012</v>
+      </c>
+      <c r="BL143" t="n">
+        <v>0.85912</v>
+      </c>
+      <c r="BM143" t="n">
+        <v>0.7534999999999999</v>
+      </c>
+      <c r="BN143" t="n">
+        <v>0.75201</v>
+      </c>
+      <c r="BO143" t="n">
+        <v>0.86141</v>
+      </c>
+      <c r="BP143" t="n">
+        <v>0.72926</v>
+      </c>
+      <c r="BQ143" t="n">
+        <v>0.76703</v>
+      </c>
+      <c r="BR143" t="n">
+        <v>0.77863</v>
+      </c>
+      <c r="BS143" t="n">
+        <v>0.77423</v>
+      </c>
+      <c r="BT143" t="n">
+        <v>0.84768</v>
+      </c>
+      <c r="BU143" t="n">
+        <v>0.8587</v>
+      </c>
+      <c r="BV143" t="n">
+        <v>0.8660399999999999</v>
+      </c>
+      <c r="BW143" t="n">
+        <v>0.8102200000000001</v>
+      </c>
+      <c r="BX143" t="n">
+        <v>1.40334</v>
+      </c>
+      <c r="BY143" t="n">
+        <v>1.12111</v>
+      </c>
+      <c r="BZ143" t="n">
+        <v>0.9389299999999999</v>
+      </c>
+      <c r="CA143" t="n">
+        <v>1.73505</v>
+      </c>
+      <c r="CB143" t="n">
+        <v>0.77276</v>
+      </c>
+      <c r="CC143" t="n">
+        <v>0.85514</v>
+      </c>
+      <c r="CD143" t="n">
+        <v>1.24385</v>
+      </c>
+      <c r="CE143" t="n">
+        <v>0.5431</v>
+      </c>
+      <c r="CF143" t="n">
+        <v>0.46032</v>
+      </c>
+      <c r="CG143" t="n">
+        <v>0.38485</v>
+      </c>
+      <c r="CH143" t="n">
+        <v>0.39507</v>
+      </c>
+      <c r="CI143" t="n">
+        <v>0.46016</v>
+      </c>
+      <c r="CJ143" t="n">
+        <v>0.38641</v>
+      </c>
+      <c r="CK143" t="n">
+        <v>0.5008</v>
+      </c>
+      <c r="CL143" t="n">
+        <v>0.39647</v>
+      </c>
+      <c r="CM143" t="n">
+        <v>0.51923</v>
+      </c>
+      <c r="CN143" t="n">
+        <v>0.46036</v>
+      </c>
+      <c r="CO143" t="n">
+        <v>0.46156</v>
+      </c>
+      <c r="CP143" t="n">
+        <v>0.4863</v>
+      </c>
+      <c r="CQ143" t="n">
+        <v>0.38594</v>
+      </c>
+      <c r="CR143" t="n">
+        <v>0.38263</v>
+      </c>
+      <c r="CS143" t="n">
+        <v>0.38366</v>
       </c>
     </row>
   </sheetData>
